--- a/research/traditional_assets/database/data/hong_kong/hong_kong_farming_agriculture.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_farming_agriculture.xlsx
@@ -1784,7 +1784,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1921,22 +1921,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07600297733566436</v>
+        <v>0.07591514742306051</v>
       </c>
       <c r="C2">
-        <v>118.8948945312233</v>
+        <v>117.9916129712505</v>
       </c>
       <c r="D2">
-        <v>84.59489453122326</v>
+        <v>84.84161297125054</v>
       </c>
       <c r="E2">
-        <v>-68.8</v>
+        <v>-67.64999999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="G2">
         <v>34.3</v>
@@ -1957,28 +1957,28 @@
         <v>6.6</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.057845</v>
       </c>
       <c r="N2">
-        <v>6.6</v>
+        <v>6.542154999999999</v>
       </c>
       <c r="O2">
-        <v>1.089</v>
+        <v>1.079455575</v>
       </c>
       <c r="P2">
-        <v>5.510999999999999</v>
+        <v>5.462699424999999</v>
       </c>
       <c r="Q2">
-        <v>11.511</v>
+        <v>11.462699425</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07600297733566436</v>
+        <v>0.07625771961925304</v>
       </c>
       <c r="T2">
-        <v>0.5887122450442503</v>
+        <v>0.5936776463029569</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>114.0980205722188</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07591514742306051</v>
+        <v>0.07582731751045667</v>
       </c>
       <c r="C3">
-        <v>117.9916129712505</v>
+        <v>117.089774714298</v>
       </c>
       <c r="D3">
-        <v>84.84161297125054</v>
+        <v>85.08977471429799</v>
       </c>
       <c r="E3">
-        <v>-67.64999999999999</v>
+        <v>-66.5</v>
       </c>
       <c r="F3">
-        <v>1.15</v>
+        <v>2.3</v>
       </c>
       <c r="G3">
         <v>34.3</v>
@@ -2039,28 +2039,28 @@
         <v>6.6</v>
       </c>
       <c r="M3">
-        <v>0.057845</v>
+        <v>0.11569</v>
       </c>
       <c r="N3">
-        <v>6.542154999999999</v>
+        <v>6.48431</v>
       </c>
       <c r="O3">
-        <v>1.079455575</v>
+        <v>1.06991115</v>
       </c>
       <c r="P3">
-        <v>5.462699424999999</v>
+        <v>5.41439885</v>
       </c>
       <c r="Q3">
-        <v>11.462699425</v>
+        <v>11.41439885</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07625771961925304</v>
+        <v>0.07651766072495578</v>
       </c>
       <c r="T3">
-        <v>0.5936776463029569</v>
+        <v>0.5987443822812288</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>114.0980205722188</v>
+        <v>57.04901028610943</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -2085,22 +2085,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07582731751045667</v>
+        <v>0.07573948759785283</v>
       </c>
       <c r="C4">
-        <v>117.089774714298</v>
+        <v>116.1893924625046</v>
       </c>
       <c r="D4">
-        <v>85.08977471429799</v>
+        <v>85.33939246250462</v>
       </c>
       <c r="E4">
-        <v>-66.5</v>
+        <v>-65.34999999999999</v>
       </c>
       <c r="F4">
-        <v>2.3</v>
+        <v>3.45</v>
       </c>
       <c r="G4">
         <v>34.3</v>
@@ -2121,28 +2121,28 @@
         <v>6.6</v>
       </c>
       <c r="M4">
-        <v>0.11569</v>
+        <v>0.173535</v>
       </c>
       <c r="N4">
-        <v>6.48431</v>
+        <v>6.426464999999999</v>
       </c>
       <c r="O4">
-        <v>1.06991115</v>
+        <v>1.060366725</v>
       </c>
       <c r="P4">
-        <v>5.41439885</v>
+        <v>5.366098275</v>
       </c>
       <c r="Q4">
-        <v>11.41439885</v>
+        <v>11.366098275</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07651766072495578</v>
+        <v>0.07678296144108539</v>
       </c>
       <c r="T4">
-        <v>0.5987443822812288</v>
+        <v>0.6039155870425581</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>57.04901028610943</v>
+        <v>38.03267352407295</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2167,22 +2167,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07573948759785283</v>
+        <v>0.07565165768524898</v>
       </c>
       <c r="C5">
-        <v>116.1893924625046</v>
+        <v>115.2904790674991</v>
       </c>
       <c r="D5">
-        <v>85.33939246250462</v>
+        <v>85.59047906749913</v>
       </c>
       <c r="E5">
-        <v>-65.34999999999999</v>
+        <v>-64.2</v>
       </c>
       <c r="F5">
-        <v>3.45</v>
+        <v>4.600000000000001</v>
       </c>
       <c r="G5">
         <v>34.3</v>
@@ -2203,28 +2203,28 @@
         <v>6.6</v>
       </c>
       <c r="M5">
-        <v>0.173535</v>
+        <v>0.23138</v>
       </c>
       <c r="N5">
-        <v>6.426464999999999</v>
+        <v>6.36862</v>
       </c>
       <c r="O5">
-        <v>1.060366725</v>
+        <v>1.0508223</v>
       </c>
       <c r="P5">
-        <v>5.366098275</v>
+        <v>5.3177977</v>
       </c>
       <c r="Q5">
-        <v>11.366098275</v>
+        <v>11.3177977</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07678296144108539</v>
+        <v>0.07705378925546769</v>
       </c>
       <c r="T5">
-        <v>0.6039155870425581</v>
+        <v>0.6091945252364149</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>38.03267352407295</v>
+        <v>28.52450514305471</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -2249,22 +2249,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07565165768524898</v>
+        <v>0.07556382777264513</v>
       </c>
       <c r="C6">
-        <v>115.2904790674991</v>
+        <v>114.3930475326053</v>
       </c>
       <c r="D6">
-        <v>85.59047906749913</v>
+        <v>85.84304753260527</v>
       </c>
       <c r="E6">
-        <v>-64.2</v>
+        <v>-63.05</v>
       </c>
       <c r="F6">
-        <v>4.600000000000001</v>
+        <v>5.75</v>
       </c>
       <c r="G6">
         <v>34.3</v>
@@ -2285,28 +2285,28 @@
         <v>6.6</v>
       </c>
       <c r="M6">
-        <v>0.23138</v>
+        <v>0.289225</v>
       </c>
       <c r="N6">
-        <v>6.36862</v>
+        <v>6.310775</v>
       </c>
       <c r="O6">
-        <v>1.0508223</v>
+        <v>1.041277875</v>
       </c>
       <c r="P6">
-        <v>5.3177977</v>
+        <v>5.269497124999999</v>
       </c>
       <c r="Q6">
-        <v>11.3177977</v>
+        <v>11.269497125</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07705378925546769</v>
+        <v>0.0773303187080475</v>
       </c>
       <c r="T6">
-        <v>0.6091945252364149</v>
+        <v>0.6145845989711951</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>28.52450514305471</v>
+        <v>22.81960411444377</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2331,22 +2331,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07556382777264513</v>
+        <v>0.07547599786004129</v>
       </c>
       <c r="C7">
-        <v>114.3930475326053</v>
+        <v>113.4971110150868</v>
       </c>
       <c r="D7">
-        <v>85.84304753260527</v>
+        <v>86.09711101508677</v>
       </c>
       <c r="E7">
-        <v>-63.05</v>
+        <v>-61.9</v>
       </c>
       <c r="F7">
-        <v>5.75</v>
+        <v>6.9</v>
       </c>
       <c r="G7">
         <v>34.3</v>
@@ -2367,28 +2367,28 @@
         <v>6.6</v>
       </c>
       <c r="M7">
-        <v>0.289225</v>
+        <v>0.34707</v>
       </c>
       <c r="N7">
-        <v>6.310775</v>
+        <v>6.252929999999999</v>
       </c>
       <c r="O7">
-        <v>1.041277875</v>
+        <v>1.03173345</v>
       </c>
       <c r="P7">
-        <v>5.269497124999999</v>
+        <v>5.221196549999999</v>
       </c>
       <c r="Q7">
-        <v>11.269497125</v>
+        <v>11.22119655</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0773303187080475</v>
+        <v>0.07761273176600136</v>
       </c>
       <c r="T7">
-        <v>0.6145845989711951</v>
+        <v>0.6200893551258642</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>22.81960411444377</v>
+        <v>19.01633676203647</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2413,22 +2413,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07547599786004128</v>
+        <v>0.07538816794743744</v>
       </c>
       <c r="C8">
-        <v>113.4971110150868</v>
+        <v>112.6026828284323</v>
       </c>
       <c r="D8">
-        <v>86.09711101508681</v>
+        <v>86.35268282843232</v>
       </c>
       <c r="E8">
-        <v>-61.9</v>
+        <v>-60.75</v>
       </c>
       <c r="F8">
-        <v>6.899999999999999</v>
+        <v>8.049999999999999</v>
       </c>
       <c r="G8">
         <v>34.3</v>
@@ -2449,28 +2449,28 @@
         <v>6.6</v>
       </c>
       <c r="M8">
-        <v>0.3470699999999999</v>
+        <v>0.4049149999999999</v>
       </c>
       <c r="N8">
-        <v>6.25293</v>
+        <v>6.195085</v>
       </c>
       <c r="O8">
-        <v>1.03173345</v>
+        <v>1.022189025</v>
       </c>
       <c r="P8">
-        <v>5.22119655</v>
+        <v>5.172895974999999</v>
       </c>
       <c r="Q8">
-        <v>11.22119655</v>
+        <v>11.172895975</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07761273176600136</v>
+        <v>0.07790121822305102</v>
       </c>
       <c r="T8">
-        <v>0.6200893551258642</v>
+        <v>0.6257124931333218</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>19.01633676203648</v>
+        <v>16.29971722460269</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2495,22 +2495,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07538816794743744</v>
+        <v>0.07530033803483359</v>
       </c>
       <c r="C9">
-        <v>112.6026828284323</v>
+        <v>111.7097764446808</v>
       </c>
       <c r="D9">
-        <v>86.35268282843232</v>
+        <v>86.60977644468085</v>
       </c>
       <c r="E9">
-        <v>-60.75</v>
+        <v>-59.59999999999999</v>
       </c>
       <c r="F9">
-        <v>8.050000000000001</v>
+        <v>9.200000000000001</v>
       </c>
       <c r="G9">
         <v>34.3</v>
@@ -2531,28 +2531,28 @@
         <v>6.6</v>
       </c>
       <c r="M9">
-        <v>0.404915</v>
+        <v>0.46276</v>
       </c>
       <c r="N9">
-        <v>6.195085</v>
+        <v>6.137239999999999</v>
       </c>
       <c r="O9">
-        <v>1.022189025</v>
+        <v>1.0126446</v>
       </c>
       <c r="P9">
-        <v>5.172895974999999</v>
+        <v>5.1245954</v>
       </c>
       <c r="Q9">
-        <v>11.172895975</v>
+        <v>11.1245954</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07790121822305102</v>
+        <v>0.07819597612481913</v>
       </c>
       <c r="T9">
-        <v>0.6257124931333219</v>
+        <v>0.6314578732713764</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>16.29971722460269</v>
+        <v>14.26225257152736</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2577,22 +2577,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07530033803483359</v>
+        <v>0.07532523312222976</v>
       </c>
       <c r="C10">
-        <v>111.7097764446808</v>
+        <v>110.4867488094704</v>
       </c>
       <c r="D10">
-        <v>86.60977644468085</v>
+        <v>86.53674880947041</v>
       </c>
       <c r="E10">
-        <v>-59.59999999999999</v>
+        <v>-58.45</v>
       </c>
       <c r="F10">
-        <v>9.200000000000001</v>
+        <v>10.35</v>
       </c>
       <c r="G10">
         <v>34.3</v>
@@ -2613,45 +2613,45 @@
         <v>6.6</v>
       </c>
       <c r="M10">
-        <v>0.46276</v>
+        <v>0.53613</v>
       </c>
       <c r="N10">
-        <v>6.137239999999999</v>
+        <v>6.06387</v>
       </c>
       <c r="O10">
-        <v>1.0126446</v>
+        <v>1.00053855</v>
       </c>
       <c r="P10">
-        <v>5.1245954</v>
+        <v>5.06333145</v>
       </c>
       <c r="Q10">
-        <v>11.1245954</v>
+        <v>11.06333145</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07819597612481913</v>
+        <v>0.07849721222223049</v>
       </c>
       <c r="T10">
-        <v>0.6314578732713764</v>
+        <v>0.6373295255003771</v>
       </c>
       <c r="U10">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.165</v>
       </c>
       <c r="W10">
-        <v>0.0420005</v>
+        <v>0.043253</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>14.26225257152736</v>
+        <v>12.31044709305579</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2659,22 +2659,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07532523312222976</v>
+        <v>0.07524992820962591</v>
       </c>
       <c r="C11">
-        <v>110.4867488094704</v>
+        <v>109.5580275256606</v>
       </c>
       <c r="D11">
-        <v>86.53674880947041</v>
+        <v>86.75802752566058</v>
       </c>
       <c r="E11">
-        <v>-58.45</v>
+        <v>-57.3</v>
       </c>
       <c r="F11">
-        <v>10.35</v>
+        <v>11.5</v>
       </c>
       <c r="G11">
         <v>34.3</v>
@@ -2695,28 +2695,28 @@
         <v>6.6</v>
       </c>
       <c r="M11">
-        <v>0.53613</v>
+        <v>0.5956999999999999</v>
       </c>
       <c r="N11">
-        <v>6.06387</v>
+        <v>6.0043</v>
       </c>
       <c r="O11">
-        <v>1.00053855</v>
+        <v>0.9907095</v>
       </c>
       <c r="P11">
-        <v>5.06333145</v>
+        <v>5.013590499999999</v>
       </c>
       <c r="Q11">
-        <v>11.06333145</v>
+        <v>11.0135905</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07849721222223049</v>
+        <v>0.07880514245513989</v>
       </c>
       <c r="T11">
-        <v>0.6373295255003771</v>
+        <v>0.6433316588900225</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2733,7 +2733,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>12.31044709305579</v>
+        <v>11.07940238375021</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2741,22 +2741,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07524992820962591</v>
+        <v>0.07517462329702206</v>
       </c>
       <c r="C12">
-        <v>109.5580275256606</v>
+        <v>108.6304407840177</v>
       </c>
       <c r="D12">
-        <v>86.75802752566058</v>
+        <v>86.98044078401767</v>
       </c>
       <c r="E12">
-        <v>-57.3</v>
+        <v>-56.15</v>
       </c>
       <c r="F12">
-        <v>11.5</v>
+        <v>12.65</v>
       </c>
       <c r="G12">
         <v>34.3</v>
@@ -2777,28 +2777,28 @@
         <v>6.6</v>
       </c>
       <c r="M12">
-        <v>0.5957</v>
+        <v>0.65527</v>
       </c>
       <c r="N12">
-        <v>6.0043</v>
+        <v>5.94473</v>
       </c>
       <c r="O12">
-        <v>0.9907095</v>
+        <v>0.98088045</v>
       </c>
       <c r="P12">
-        <v>5.013590499999999</v>
+        <v>4.96384955</v>
       </c>
       <c r="Q12">
-        <v>11.0135905</v>
+        <v>10.96384955</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07880514245513989</v>
+        <v>0.0791199924685641</v>
       </c>
       <c r="T12">
-        <v>0.6433316588900225</v>
+        <v>0.6494686716816822</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.07940238375021</v>
+        <v>10.07218398522746</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2823,22 +2823,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07517462329702206</v>
+        <v>0.07526965838441821</v>
       </c>
       <c r="C13">
-        <v>108.6304407840177</v>
+        <v>107.1999423240818</v>
       </c>
       <c r="D13">
-        <v>86.98044078401767</v>
+        <v>86.69994232408182</v>
       </c>
       <c r="E13">
-        <v>-56.15</v>
+        <v>-55</v>
       </c>
       <c r="F13">
-        <v>12.65</v>
+        <v>13.8</v>
       </c>
       <c r="G13">
         <v>34.3</v>
@@ -2859,45 +2859,45 @@
         <v>6.6</v>
       </c>
       <c r="M13">
-        <v>0.65527</v>
+        <v>0.7383</v>
       </c>
       <c r="N13">
-        <v>5.94473</v>
+        <v>5.8617</v>
       </c>
       <c r="O13">
-        <v>0.98088045</v>
+        <v>0.9671805</v>
       </c>
       <c r="P13">
-        <v>4.96384955</v>
+        <v>4.894519499999999</v>
       </c>
       <c r="Q13">
-        <v>10.96384955</v>
+        <v>10.8945195</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0791199924685641</v>
+        <v>0.0794419981641116</v>
       </c>
       <c r="T13">
-        <v>0.6494686716816822</v>
+        <v>0.6557451620367888</v>
       </c>
       <c r="U13">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V13">
         <v>0.165</v>
       </c>
       <c r="W13">
-        <v>0.043253</v>
+        <v>0.0446725</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>10.07218398522746</v>
+        <v>8.939455505891914</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2905,22 +2905,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07526965838441821</v>
+        <v>0.07520854847181437</v>
       </c>
       <c r="C14">
-        <v>107.1999423240818</v>
+        <v>106.2301017054012</v>
       </c>
       <c r="D14">
-        <v>86.69994232408182</v>
+        <v>86.88010170540119</v>
       </c>
       <c r="E14">
-        <v>-55</v>
+        <v>-53.84999999999999</v>
       </c>
       <c r="F14">
-        <v>13.8</v>
+        <v>14.95</v>
       </c>
       <c r="G14">
         <v>34.3</v>
@@ -2941,28 +2941,28 @@
         <v>6.6</v>
       </c>
       <c r="M14">
-        <v>0.7383</v>
+        <v>0.799825</v>
       </c>
       <c r="N14">
-        <v>5.8617</v>
+        <v>5.800174999999999</v>
       </c>
       <c r="O14">
-        <v>0.9671805</v>
+        <v>0.957028875</v>
       </c>
       <c r="P14">
-        <v>4.894519499999999</v>
+        <v>4.843146125</v>
       </c>
       <c r="Q14">
-        <v>10.8945195</v>
+        <v>10.843146125</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0794419981641116</v>
+        <v>0.07977140628944179</v>
       </c>
       <c r="T14">
-        <v>0.6557451620367888</v>
+        <v>0.6621659395264956</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2979,7 +2979,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>8.939455505891914</v>
+        <v>8.251805082361766</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2987,22 +2987,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07520854847181437</v>
+        <v>0.07514743855921052</v>
       </c>
       <c r="C15">
-        <v>106.2301017054012</v>
+        <v>105.2610113753037</v>
       </c>
       <c r="D15">
-        <v>86.88010170540119</v>
+        <v>87.06101137530366</v>
       </c>
       <c r="E15">
-        <v>-53.84999999999999</v>
+        <v>-52.7</v>
       </c>
       <c r="F15">
-        <v>14.95</v>
+        <v>16.1</v>
       </c>
       <c r="G15">
         <v>34.3</v>
@@ -3023,28 +3023,28 @@
         <v>6.6</v>
       </c>
       <c r="M15">
-        <v>0.799825</v>
+        <v>0.8613500000000001</v>
       </c>
       <c r="N15">
-        <v>5.800174999999999</v>
+        <v>5.73865</v>
       </c>
       <c r="O15">
-        <v>0.957028875</v>
+        <v>0.94687725</v>
       </c>
       <c r="P15">
-        <v>4.843146125</v>
+        <v>4.79177275</v>
       </c>
       <c r="Q15">
-        <v>10.843146125</v>
+        <v>10.79177275</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07977140628944179</v>
+        <v>0.08010847506884944</v>
       </c>
       <c r="T15">
-        <v>0.6621659395264956</v>
+        <v>0.6687360374229397</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -3061,7 +3061,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.251805082361766</v>
+        <v>7.66239043362164</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07514743855921052</v>
+        <v>0.07518652864660667</v>
       </c>
       <c r="C16">
-        <v>105.2610113753037</v>
+        <v>103.9952024417483</v>
       </c>
       <c r="D16">
-        <v>87.06101137530366</v>
+        <v>86.94520244174829</v>
       </c>
       <c r="E16">
-        <v>-52.7</v>
+        <v>-51.55</v>
       </c>
       <c r="F16">
-        <v>16.1</v>
+        <v>17.25</v>
       </c>
       <c r="G16">
         <v>34.3</v>
@@ -3105,45 +3105,45 @@
         <v>6.6</v>
       </c>
       <c r="M16">
-        <v>0.8613500000000001</v>
+        <v>0.9366750000000003</v>
       </c>
       <c r="N16">
-        <v>5.73865</v>
+        <v>5.663324999999999</v>
       </c>
       <c r="O16">
-        <v>0.94687725</v>
+        <v>0.9344486249999999</v>
       </c>
       <c r="P16">
-        <v>4.79177275</v>
+        <v>4.728876375</v>
       </c>
       <c r="Q16">
-        <v>10.79177275</v>
+        <v>10.728876375</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08010847506884944</v>
+        <v>0.0804534748783608</v>
       </c>
       <c r="T16">
-        <v>0.6687360374229397</v>
+        <v>0.6754607258581238</v>
       </c>
       <c r="U16">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V16">
         <v>0.165</v>
       </c>
       <c r="W16">
-        <v>0.0446725</v>
+        <v>0.0453405</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y16">
-        <v>7.66239043362164</v>
+        <v>7.046200656577787</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -3151,22 +3151,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07518652864660667</v>
+        <v>0.07513209873400281</v>
       </c>
       <c r="C17">
-        <v>103.9952024417483</v>
+        <v>103.0065417244619</v>
       </c>
       <c r="D17">
-        <v>86.94520244174829</v>
+        <v>87.10654172446192</v>
       </c>
       <c r="E17">
-        <v>-51.55</v>
+        <v>-50.39999999999999</v>
       </c>
       <c r="F17">
-        <v>17.25</v>
+        <v>18.4</v>
       </c>
       <c r="G17">
         <v>34.3</v>
@@ -3187,28 +3187,28 @@
         <v>6.6</v>
       </c>
       <c r="M17">
-        <v>0.936675</v>
+        <v>0.9991200000000001</v>
       </c>
       <c r="N17">
-        <v>5.663324999999999</v>
+        <v>5.600879999999999</v>
       </c>
       <c r="O17">
-        <v>0.9344486249999999</v>
+        <v>0.9241451999999999</v>
       </c>
       <c r="P17">
-        <v>4.728876375</v>
+        <v>4.676734799999999</v>
       </c>
       <c r="Q17">
-        <v>10.728876375</v>
+        <v>10.6767348</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0804534748783608</v>
+        <v>0.08080668896905098</v>
       </c>
       <c r="T17">
-        <v>0.6754607258581238</v>
+        <v>0.6823455259227169</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.046200656577787</v>
+        <v>6.605813115541675</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -3233,22 +3233,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07513209873400281</v>
+        <v>0.07507766882139896</v>
       </c>
       <c r="C18">
-        <v>103.0065417244619</v>
+        <v>102.0184808966757</v>
       </c>
       <c r="D18">
-        <v>87.10654172446192</v>
+        <v>87.26848089667568</v>
       </c>
       <c r="E18">
-        <v>-50.39999999999999</v>
+        <v>-49.25</v>
       </c>
       <c r="F18">
-        <v>18.4</v>
+        <v>19.55</v>
       </c>
       <c r="G18">
         <v>34.3</v>
@@ -3269,28 +3269,28 @@
         <v>6.6</v>
       </c>
       <c r="M18">
-        <v>0.9991200000000001</v>
+        <v>1.061565</v>
       </c>
       <c r="N18">
-        <v>5.600879999999999</v>
+        <v>5.538435</v>
       </c>
       <c r="O18">
-        <v>0.9241451999999999</v>
+        <v>0.913841775</v>
       </c>
       <c r="P18">
-        <v>4.676734799999999</v>
+        <v>4.624593225</v>
       </c>
       <c r="Q18">
-        <v>10.6767348</v>
+        <v>10.624593225</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08080668896905098</v>
+        <v>0.08116841424264937</v>
       </c>
       <c r="T18">
-        <v>0.6823455259227169</v>
+        <v>0.6893962247840472</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -3307,7 +3307,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>6.605813115541675</v>
+        <v>6.217235873450989</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3315,22 +3315,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07507766882139896</v>
+        <v>0.07517353890879513</v>
       </c>
       <c r="C19">
-        <v>102.0184808966757</v>
+        <v>100.5836518566178</v>
       </c>
       <c r="D19">
-        <v>87.26848089667568</v>
+        <v>86.9836518566178</v>
       </c>
       <c r="E19">
-        <v>-49.25</v>
+        <v>-48.09999999999999</v>
       </c>
       <c r="F19">
-        <v>19.55</v>
+        <v>20.7</v>
       </c>
       <c r="G19">
         <v>34.3</v>
@@ -3351,45 +3351,45 @@
         <v>6.6</v>
       </c>
       <c r="M19">
-        <v>1.061565</v>
+        <v>1.14471</v>
       </c>
       <c r="N19">
-        <v>5.538435</v>
+        <v>5.45529</v>
       </c>
       <c r="O19">
-        <v>0.913841775</v>
+        <v>0.90012285</v>
       </c>
       <c r="P19">
-        <v>4.624593225</v>
+        <v>4.55516715</v>
       </c>
       <c r="Q19">
-        <v>10.624593225</v>
+        <v>10.55516715</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08116841424264937</v>
+        <v>0.08153896208389649</v>
       </c>
       <c r="T19">
-        <v>0.6893962247840472</v>
+        <v>0.6966188919102879</v>
       </c>
       <c r="U19">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V19">
         <v>0.165</v>
       </c>
       <c r="W19">
-        <v>0.0453405</v>
+        <v>0.0461755</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y19">
-        <v>6.217235873450989</v>
+        <v>5.765652435988153</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3397,22 +3397,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07517353890879513</v>
+        <v>0.07512745899619128</v>
       </c>
       <c r="C20">
-        <v>100.5836518566178</v>
+        <v>99.57032237676199</v>
       </c>
       <c r="D20">
-        <v>86.9836518566178</v>
+        <v>87.120322376762</v>
       </c>
       <c r="E20">
-        <v>-48.09999999999999</v>
+        <v>-46.95</v>
       </c>
       <c r="F20">
-        <v>20.7</v>
+        <v>21.85</v>
       </c>
       <c r="G20">
         <v>34.3</v>
@@ -3433,28 +3433,28 @@
         <v>6.6</v>
       </c>
       <c r="M20">
-        <v>1.14471</v>
+        <v>1.208305</v>
       </c>
       <c r="N20">
-        <v>5.45529</v>
+        <v>5.391694999999999</v>
       </c>
       <c r="O20">
-        <v>0.90012285</v>
+        <v>0.8896296749999999</v>
       </c>
       <c r="P20">
-        <v>4.55516715</v>
+        <v>4.502065324999999</v>
       </c>
       <c r="Q20">
-        <v>10.55516715</v>
+        <v>10.502065325</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08153896208389649</v>
+        <v>0.08191865925455713</v>
       </c>
       <c r="T20">
-        <v>0.6966188919102879</v>
+        <v>0.7040198964964359</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.765652435988154</v>
+        <v>5.462197044620355</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3479,22 +3479,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07512745899619128</v>
+        <v>0.07508137908358743</v>
       </c>
       <c r="C21">
-        <v>99.57032237676199</v>
+        <v>98.55742305189344</v>
       </c>
       <c r="D21">
-        <v>87.120322376762</v>
+        <v>87.25742305189344</v>
       </c>
       <c r="E21">
-        <v>-46.95</v>
+        <v>-45.8</v>
       </c>
       <c r="F21">
-        <v>21.85</v>
+        <v>23</v>
       </c>
       <c r="G21">
         <v>34.3</v>
@@ -3515,28 +3515,28 @@
         <v>6.6</v>
       </c>
       <c r="M21">
-        <v>1.208305</v>
+        <v>1.2719</v>
       </c>
       <c r="N21">
-        <v>5.391694999999999</v>
+        <v>5.328099999999999</v>
       </c>
       <c r="O21">
-        <v>0.8896296749999999</v>
+        <v>0.8791364999999999</v>
       </c>
       <c r="P21">
-        <v>4.502065324999999</v>
+        <v>4.4489635</v>
       </c>
       <c r="Q21">
-        <v>10.502065325</v>
+        <v>10.4489635</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08191865925455713</v>
+        <v>0.08230784885448429</v>
       </c>
       <c r="T21">
-        <v>0.7040198964964359</v>
+        <v>0.7116059261972376</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.462197044620355</v>
+        <v>5.189087192389338</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3561,22 +3561,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07508137908358743</v>
+        <v>0.07503529917098359</v>
       </c>
       <c r="C22">
-        <v>98.55742305189344</v>
+        <v>97.54495591600924</v>
       </c>
       <c r="D22">
-        <v>87.25742305189344</v>
+        <v>87.39495591600925</v>
       </c>
       <c r="E22">
-        <v>-45.8</v>
+        <v>-44.64999999999999</v>
       </c>
       <c r="F22">
-        <v>23</v>
+        <v>24.15</v>
       </c>
       <c r="G22">
         <v>34.3</v>
@@ -3597,28 +3597,28 @@
         <v>6.6</v>
       </c>
       <c r="M22">
-        <v>1.2719</v>
+        <v>1.335495</v>
       </c>
       <c r="N22">
-        <v>5.328099999999999</v>
+        <v>5.264505</v>
       </c>
       <c r="O22">
-        <v>0.8791364999999999</v>
+        <v>0.868643325</v>
       </c>
       <c r="P22">
-        <v>4.4489635</v>
+        <v>4.395861675</v>
       </c>
       <c r="Q22">
-        <v>10.4489635</v>
+        <v>10.395861675</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08230784885448429</v>
+        <v>0.08270689135567542</v>
       </c>
       <c r="T22">
-        <v>0.7116059261972376</v>
+        <v>0.7193840072828697</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3635,7 +3635,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.189087192389338</v>
+        <v>4.941987802275561</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3643,22 +3643,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07503529917098359</v>
+        <v>0.07498921925837974</v>
       </c>
       <c r="C23">
-        <v>97.54495591600926</v>
+        <v>96.53292301595046</v>
       </c>
       <c r="D23">
-        <v>87.39495591600925</v>
+        <v>87.53292301595046</v>
       </c>
       <c r="E23">
-        <v>-44.65</v>
+        <v>-43.5</v>
       </c>
       <c r="F23">
-        <v>24.15</v>
+        <v>25.3</v>
       </c>
       <c r="G23">
         <v>34.3</v>
@@ -3679,28 +3679,28 @@
         <v>6.6</v>
       </c>
       <c r="M23">
-        <v>1.335495</v>
+        <v>1.39909</v>
       </c>
       <c r="N23">
-        <v>5.264505</v>
+        <v>5.200909999999999</v>
       </c>
       <c r="O23">
-        <v>0.868643325</v>
+        <v>0.8581501499999999</v>
       </c>
       <c r="P23">
-        <v>4.395861675</v>
+        <v>4.342759849999999</v>
       </c>
       <c r="Q23">
-        <v>10.395861675</v>
+        <v>10.34275985</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08270689135567542</v>
+        <v>0.08311616571587147</v>
       </c>
       <c r="T23">
-        <v>0.7193840072828697</v>
+        <v>0.7273615263450565</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.941987802275561</v>
+        <v>4.717351993081216</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3725,22 +3725,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07498921925837974</v>
+        <v>0.0749431393457759</v>
       </c>
       <c r="C24">
-        <v>96.53292301595046</v>
+        <v>95.52132641150359</v>
       </c>
       <c r="D24">
-        <v>87.53292301595046</v>
+        <v>87.6713264115036</v>
       </c>
       <c r="E24">
-        <v>-43.5</v>
+        <v>-42.34999999999999</v>
       </c>
       <c r="F24">
-        <v>25.3</v>
+        <v>26.45</v>
       </c>
       <c r="G24">
         <v>34.3</v>
@@ -3761,28 +3761,28 @@
         <v>6.6</v>
       </c>
       <c r="M24">
-        <v>1.39909</v>
+        <v>1.462685</v>
       </c>
       <c r="N24">
-        <v>5.200909999999999</v>
+        <v>5.137314999999999</v>
       </c>
       <c r="O24">
-        <v>0.8581501499999999</v>
+        <v>0.8476569749999999</v>
       </c>
       <c r="P24">
-        <v>4.342759849999999</v>
+        <v>4.289658025</v>
       </c>
       <c r="Q24">
-        <v>10.34275985</v>
+        <v>10.289658025</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08311616571587147</v>
+        <v>0.08353607057892973</v>
       </c>
       <c r="T24">
-        <v>0.7273615263450565</v>
+        <v>0.7355462536945727</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3799,7 +3799,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.717351993081216</v>
+        <v>4.512249732512467</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3807,22 +3807,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0749431393457759</v>
+        <v>0.07539805943317204</v>
       </c>
       <c r="C25">
-        <v>95.52132641150359</v>
+        <v>93.02382430369454</v>
       </c>
       <c r="D25">
-        <v>87.6713264115036</v>
+        <v>86.32382430369455</v>
       </c>
       <c r="E25">
-        <v>-42.34999999999999</v>
+        <v>-41.2</v>
       </c>
       <c r="F25">
-        <v>26.45</v>
+        <v>27.6</v>
       </c>
       <c r="G25">
         <v>34.3</v>
@@ -3843,45 +3843,45 @@
         <v>6.6</v>
       </c>
       <c r="M25">
-        <v>1.462685</v>
+        <v>1.59528</v>
       </c>
       <c r="N25">
-        <v>5.137314999999999</v>
+        <v>5.004719999999999</v>
       </c>
       <c r="O25">
-        <v>0.8476569749999999</v>
+        <v>0.8257787999999998</v>
       </c>
       <c r="P25">
-        <v>4.289658025</v>
+        <v>4.178941199999999</v>
       </c>
       <c r="Q25">
-        <v>10.289658025</v>
+        <v>10.1789412</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08353607057892973</v>
+        <v>0.08396702556996322</v>
       </c>
       <c r="T25">
-        <v>0.7355462536945727</v>
+        <v>0.7439463686059185</v>
       </c>
       <c r="U25">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V25">
         <v>0.165</v>
       </c>
       <c r="W25">
-        <v>0.0461755</v>
+        <v>0.048263</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y25">
-        <v>4.512249732512467</v>
+        <v>4.137204754024371</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3889,22 +3889,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07539805943317204</v>
+        <v>0.0761034795205682</v>
       </c>
       <c r="C26">
-        <v>93.02382430369455</v>
+        <v>89.86433362314907</v>
       </c>
       <c r="D26">
-        <v>86.32382430369455</v>
+        <v>84.31433362314907</v>
       </c>
       <c r="E26">
-        <v>-41.2</v>
+        <v>-40.05</v>
       </c>
       <c r="F26">
-        <v>27.6</v>
+        <v>28.75</v>
       </c>
       <c r="G26">
         <v>34.3</v>
@@ -3925,45 +3925,45 @@
         <v>6.6</v>
       </c>
       <c r="M26">
-        <v>1.59528</v>
+        <v>1.762375</v>
       </c>
       <c r="N26">
-        <v>5.00472</v>
+        <v>4.837624999999999</v>
       </c>
       <c r="O26">
-        <v>0.8257788</v>
+        <v>0.7982081249999999</v>
       </c>
       <c r="P26">
-        <v>4.1789412</v>
+        <v>4.039416874999999</v>
       </c>
       <c r="Q26">
-        <v>10.1789412</v>
+        <v>10.039416875</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08396702556996322</v>
+        <v>0.08440947269409094</v>
       </c>
       <c r="T26">
-        <v>0.7439463686059185</v>
+        <v>0.7525704865815667</v>
       </c>
       <c r="U26">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V26">
         <v>0.165</v>
       </c>
       <c r="W26">
-        <v>0.048263</v>
+        <v>0.05118549999999999</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>4.137204754024372</v>
+        <v>3.744946450102844</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3971,22 +3971,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0761034795205682</v>
+        <v>0.07610749960796435</v>
       </c>
       <c r="C27">
-        <v>89.86433362314907</v>
+        <v>88.70314988993788</v>
       </c>
       <c r="D27">
-        <v>84.31433362314907</v>
+        <v>84.30314988993788</v>
       </c>
       <c r="E27">
-        <v>-40.05</v>
+        <v>-38.89999999999999</v>
       </c>
       <c r="F27">
-        <v>28.75</v>
+        <v>29.9</v>
       </c>
       <c r="G27">
         <v>34.3</v>
@@ -4007,28 +4007,28 @@
         <v>6.6</v>
       </c>
       <c r="M27">
-        <v>1.762375</v>
+        <v>1.83287</v>
       </c>
       <c r="N27">
-        <v>4.837624999999999</v>
+        <v>4.76713</v>
       </c>
       <c r="O27">
-        <v>0.7982081249999999</v>
+        <v>0.78657645</v>
       </c>
       <c r="P27">
-        <v>4.039416874999999</v>
+        <v>3.98055355</v>
       </c>
       <c r="Q27">
-        <v>10.039416875</v>
+        <v>9.98055355</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08440947269409094</v>
+        <v>0.08486387784860047</v>
       </c>
       <c r="T27">
-        <v>0.7525704865815667</v>
+        <v>0.761427688826827</v>
       </c>
       <c r="U27">
         <v>0.0613</v>
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.744946450102844</v>
+        <v>3.600910048175811</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -4053,22 +4053,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07610749960796435</v>
+        <v>0.0767427796953605</v>
       </c>
       <c r="C28">
-        <v>88.70314988993788</v>
+        <v>85.82233860028893</v>
       </c>
       <c r="D28">
-        <v>84.30314988993788</v>
+        <v>82.57233860028893</v>
       </c>
       <c r="E28">
-        <v>-38.89999999999999</v>
+        <v>-37.75</v>
       </c>
       <c r="F28">
-        <v>29.9</v>
+        <v>31.05</v>
       </c>
       <c r="G28">
         <v>34.3</v>
@@ -4089,45 +4089,45 @@
         <v>6.6</v>
       </c>
       <c r="M28">
-        <v>1.83287</v>
+        <v>1.990305</v>
       </c>
       <c r="N28">
-        <v>4.76713</v>
+        <v>4.609694999999999</v>
       </c>
       <c r="O28">
-        <v>0.78657645</v>
+        <v>0.7605996749999999</v>
       </c>
       <c r="P28">
-        <v>3.98055355</v>
+        <v>3.849095325</v>
       </c>
       <c r="Q28">
-        <v>9.98055355</v>
+        <v>9.849095325</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08486387784860047</v>
+        <v>0.08533073245939796</v>
       </c>
       <c r="T28">
-        <v>0.761427688826827</v>
+        <v>0.7705275541473</v>
       </c>
       <c r="U28">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V28">
         <v>0.165</v>
       </c>
       <c r="W28">
-        <v>0.05118549999999999</v>
+        <v>0.0535235</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>3.600910048175811</v>
+        <v>3.316074671972386</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.0767427796953605</v>
+        <v>0.07677017978275667</v>
       </c>
       <c r="C29">
-        <v>85.82233860028893</v>
+        <v>84.59928480111746</v>
       </c>
       <c r="D29">
-        <v>82.57233860028893</v>
+        <v>82.49928480111747</v>
       </c>
       <c r="E29">
-        <v>-37.75</v>
+        <v>-36.59999999999999</v>
       </c>
       <c r="F29">
-        <v>31.05</v>
+        <v>32.2</v>
       </c>
       <c r="G29">
         <v>34.3</v>
@@ -4171,28 +4171,28 @@
         <v>6.6</v>
       </c>
       <c r="M29">
-        <v>1.990305</v>
+        <v>2.06402</v>
       </c>
       <c r="N29">
-        <v>4.609694999999999</v>
+        <v>4.535979999999999</v>
       </c>
       <c r="O29">
-        <v>0.7605996749999999</v>
+        <v>0.7484367</v>
       </c>
       <c r="P29">
-        <v>3.849095325</v>
+        <v>3.787543299999999</v>
       </c>
       <c r="Q29">
-        <v>9.849095325</v>
+        <v>9.787543299999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08533073245939796</v>
+        <v>0.0858105552538287</v>
       </c>
       <c r="T29">
-        <v>0.7705275541473</v>
+        <v>0.7798801935044528</v>
       </c>
       <c r="U29">
         <v>0.0641</v>
@@ -4209,7 +4209,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.316074671972386</v>
+        <v>3.197643433687658</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -4217,22 +4217,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07677017978275667</v>
+        <v>0.07679757987015282</v>
       </c>
       <c r="C30">
-        <v>84.59928480111746</v>
+        <v>83.37636015270493</v>
       </c>
       <c r="D30">
-        <v>82.49928480111747</v>
+        <v>82.42636015270493</v>
       </c>
       <c r="E30">
-        <v>-36.59999999999999</v>
+        <v>-35.45</v>
       </c>
       <c r="F30">
-        <v>32.2</v>
+        <v>33.35</v>
       </c>
       <c r="G30">
         <v>34.3</v>
@@ -4253,28 +4253,28 @@
         <v>6.6</v>
       </c>
       <c r="M30">
-        <v>2.06402</v>
+        <v>2.137735</v>
       </c>
       <c r="N30">
-        <v>4.535979999999999</v>
+        <v>4.462264999999999</v>
       </c>
       <c r="O30">
-        <v>0.7484367</v>
+        <v>0.736273725</v>
       </c>
       <c r="P30">
-        <v>3.787543299999999</v>
+        <v>3.725991274999999</v>
       </c>
       <c r="Q30">
-        <v>9.787543299999999</v>
+        <v>9.725991274999998</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.0858105552538287</v>
+        <v>0.08630389418331383</v>
       </c>
       <c r="T30">
-        <v>0.7798801935044528</v>
+        <v>0.7894962874913845</v>
       </c>
       <c r="U30">
         <v>0.0641</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.197643433687658</v>
+        <v>3.087379867008773</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4299,22 +4299,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07679757987015282</v>
+        <v>0.07877887995754895</v>
       </c>
       <c r="C31">
-        <v>83.37636015270493</v>
+        <v>77.27436194098527</v>
       </c>
       <c r="D31">
-        <v>82.42636015270493</v>
+        <v>77.47436194098528</v>
       </c>
       <c r="E31">
-        <v>-35.45</v>
+        <v>-34.3</v>
       </c>
       <c r="F31">
-        <v>33.34999999999999</v>
+        <v>34.5</v>
       </c>
       <c r="G31">
         <v>34.3</v>
@@ -4335,45 +4335,45 @@
         <v>6.6</v>
       </c>
       <c r="M31">
-        <v>2.137735</v>
+        <v>2.48055</v>
       </c>
       <c r="N31">
-        <v>4.462265</v>
+        <v>4.11945</v>
       </c>
       <c r="O31">
-        <v>0.7362737250000001</v>
+        <v>0.6797092499999999</v>
       </c>
       <c r="P31">
-        <v>3.725991275</v>
+        <v>3.439740749999999</v>
       </c>
       <c r="Q31">
-        <v>9.725991275</v>
+        <v>9.439740749999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08630389418331383</v>
+        <v>0.08681132851078424</v>
       </c>
       <c r="T31">
-        <v>0.7894962874913845</v>
+        <v>0.7993871270207999</v>
       </c>
       <c r="U31">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V31">
         <v>0.165</v>
       </c>
       <c r="W31">
-        <v>0.0535235</v>
+        <v>0.0600365</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>3.087379867008774</v>
+        <v>2.660700247928887</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4381,22 +4381,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07877887995754895</v>
+        <v>0.07887141004494513</v>
       </c>
       <c r="C32">
-        <v>77.27436194098527</v>
+        <v>75.90759738599289</v>
       </c>
       <c r="D32">
-        <v>77.47436194098528</v>
+        <v>77.2575973859929</v>
       </c>
       <c r="E32">
-        <v>-34.3</v>
+        <v>-33.15</v>
       </c>
       <c r="F32">
-        <v>34.5</v>
+        <v>35.65</v>
       </c>
       <c r="G32">
         <v>34.3</v>
@@ -4417,28 +4417,28 @@
         <v>6.6</v>
       </c>
       <c r="M32">
-        <v>2.48055</v>
+        <v>2.563235</v>
       </c>
       <c r="N32">
-        <v>4.11945</v>
+        <v>4.036764999999999</v>
       </c>
       <c r="O32">
-        <v>0.6797092499999999</v>
+        <v>0.6660662249999999</v>
       </c>
       <c r="P32">
-        <v>3.439740749999999</v>
+        <v>3.370698774999999</v>
       </c>
       <c r="Q32">
-        <v>9.439740749999999</v>
+        <v>9.370698774999999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08681132851078424</v>
+        <v>0.08733347107963063</v>
       </c>
       <c r="T32">
-        <v>0.7993871270207999</v>
+        <v>0.8095646575510681</v>
       </c>
       <c r="U32">
         <v>0.07190000000000001</v>
@@ -4455,7 +4455,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.660700247928887</v>
+        <v>2.574871207673116</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4463,22 +4463,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07887141004494513</v>
+        <v>0.08000602013234129</v>
       </c>
       <c r="C33">
-        <v>75.90759738599289</v>
+        <v>72.19497101253592</v>
       </c>
       <c r="D33">
-        <v>77.2575973859929</v>
+        <v>74.69497101253593</v>
       </c>
       <c r="E33">
-        <v>-33.15</v>
+        <v>-31.99999999999999</v>
       </c>
       <c r="F33">
-        <v>35.65</v>
+        <v>36.8</v>
       </c>
       <c r="G33">
         <v>34.3</v>
@@ -4499,45 +4499,45 @@
         <v>6.6</v>
       </c>
       <c r="M33">
-        <v>2.563235</v>
+        <v>2.78944</v>
       </c>
       <c r="N33">
-        <v>4.036764999999999</v>
+        <v>3.810559999999999</v>
       </c>
       <c r="O33">
-        <v>0.6660662249999999</v>
+        <v>0.6287423999999999</v>
       </c>
       <c r="P33">
-        <v>3.370698774999999</v>
+        <v>3.1818176</v>
       </c>
       <c r="Q33">
-        <v>9.370698774999999</v>
+        <v>9.181817599999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08733347107963063</v>
+        <v>0.08787097078285483</v>
       </c>
       <c r="T33">
-        <v>0.8095646575510681</v>
+        <v>0.8200415272145793</v>
       </c>
       <c r="U33">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V33">
         <v>0.165</v>
       </c>
       <c r="W33">
-        <v>0.0600365</v>
+        <v>0.063293</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y33">
-        <v>2.574871207673116</v>
+        <v>2.366066307215785</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4545,22 +4545,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08000602013234129</v>
+        <v>0.08013111521973743</v>
       </c>
       <c r="C34">
-        <v>72.19497101253592</v>
+        <v>70.77279884839098</v>
       </c>
       <c r="D34">
-        <v>74.69497101253593</v>
+        <v>74.42279884839098</v>
       </c>
       <c r="E34">
-        <v>-31.99999999999999</v>
+        <v>-30.84999999999999</v>
       </c>
       <c r="F34">
-        <v>36.8</v>
+        <v>37.95</v>
       </c>
       <c r="G34">
         <v>34.3</v>
@@ -4581,28 +4581,28 @@
         <v>6.6</v>
       </c>
       <c r="M34">
-        <v>2.78944</v>
+        <v>2.87661</v>
       </c>
       <c r="N34">
-        <v>3.810559999999999</v>
+        <v>3.723389999999999</v>
       </c>
       <c r="O34">
-        <v>0.6287423999999999</v>
+        <v>0.61435935</v>
       </c>
       <c r="P34">
-        <v>3.1818176</v>
+        <v>3.109030649999999</v>
       </c>
       <c r="Q34">
-        <v>9.181817599999999</v>
+        <v>9.109030649999999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08787097078285483</v>
+        <v>0.08842451525333946</v>
       </c>
       <c r="T34">
-        <v>0.8200415272145793</v>
+        <v>0.8308311392561059</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.366066307215785</v>
+        <v>2.294367328209246</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4627,22 +4627,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08013111521973743</v>
+        <v>0.08025621030713359</v>
       </c>
       <c r="C35">
-        <v>70.77279884839098</v>
+        <v>69.35260295501732</v>
       </c>
       <c r="D35">
-        <v>74.42279884839098</v>
+        <v>74.15260295501733</v>
       </c>
       <c r="E35">
-        <v>-30.84999999999999</v>
+        <v>-29.7</v>
       </c>
       <c r="F35">
-        <v>37.95</v>
+        <v>39.1</v>
       </c>
       <c r="G35">
         <v>34.3</v>
@@ -4663,28 +4663,28 @@
         <v>6.6</v>
       </c>
       <c r="M35">
-        <v>2.87661</v>
+        <v>2.96378</v>
       </c>
       <c r="N35">
-        <v>3.723389999999999</v>
+        <v>3.636219999999999</v>
       </c>
       <c r="O35">
-        <v>0.61435935</v>
+        <v>0.5999762999999999</v>
       </c>
       <c r="P35">
-        <v>3.109030649999999</v>
+        <v>3.0362437</v>
       </c>
       <c r="Q35">
-        <v>9.109030649999999</v>
+        <v>9.0362437</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08842451525333946</v>
+        <v>0.08899483379868725</v>
       </c>
       <c r="T35">
-        <v>0.8308311392561059</v>
+        <v>0.8419477092382848</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.294367328209246</v>
+        <v>2.226885936203092</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4709,22 +4709,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08025621030713359</v>
+        <v>0.08038130539452974</v>
       </c>
       <c r="C36">
-        <v>69.35260295501732</v>
+        <v>67.93436188541392</v>
       </c>
       <c r="D36">
-        <v>74.15260295501733</v>
+        <v>73.88436188541394</v>
       </c>
       <c r="E36">
-        <v>-29.7</v>
+        <v>-28.54999999999999</v>
       </c>
       <c r="F36">
-        <v>39.1</v>
+        <v>40.25000000000001</v>
       </c>
       <c r="G36">
         <v>34.3</v>
@@ -4745,28 +4745,28 @@
         <v>6.6</v>
       </c>
       <c r="M36">
-        <v>2.96378</v>
+        <v>3.050950000000001</v>
       </c>
       <c r="N36">
-        <v>3.636219999999999</v>
+        <v>3.549049999999999</v>
       </c>
       <c r="O36">
-        <v>0.5999762999999999</v>
+        <v>0.5855932499999998</v>
       </c>
       <c r="P36">
-        <v>3.0362437</v>
+        <v>2.963456749999999</v>
       </c>
       <c r="Q36">
-        <v>9.0362437</v>
+        <v>8.963456749999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08899483379868725</v>
+        <v>0.08958270060696884</v>
       </c>
       <c r="T36">
-        <v>0.8419477092382848</v>
+        <v>0.8534063275276076</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4783,7 +4783,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.226885936203092</v>
+        <v>2.163260623740146</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4791,22 +4791,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08038130539452974</v>
+        <v>0.08050640048192589</v>
       </c>
       <c r="C37">
-        <v>67.93436188541392</v>
+        <v>66.51805450179234</v>
       </c>
       <c r="D37">
-        <v>73.88436188541394</v>
+        <v>73.61805450179234</v>
       </c>
       <c r="E37">
-        <v>-28.54999999999999</v>
+        <v>-27.39999999999999</v>
       </c>
       <c r="F37">
-        <v>40.25000000000001</v>
+        <v>41.40000000000001</v>
       </c>
       <c r="G37">
         <v>34.3</v>
@@ -4827,28 +4827,28 @@
         <v>6.6</v>
       </c>
       <c r="M37">
-        <v>3.050950000000001</v>
+        <v>3.138120000000001</v>
       </c>
       <c r="N37">
-        <v>3.549049999999999</v>
+        <v>3.461879999999999</v>
       </c>
       <c r="O37">
-        <v>0.5855932499999998</v>
+        <v>0.5712101999999999</v>
       </c>
       <c r="P37">
-        <v>2.963456749999999</v>
+        <v>2.890669799999999</v>
       </c>
       <c r="Q37">
-        <v>8.963456749999999</v>
+        <v>8.8906698</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08958270060696884</v>
+        <v>0.09018893825300922</v>
       </c>
       <c r="T37">
-        <v>0.8534063275276076</v>
+        <v>0.8652230276384717</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4865,7 +4865,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.163260623740146</v>
+        <v>2.103170050858475</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4873,22 +4873,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08050640048192591</v>
+        <v>0.08063149556932206</v>
       </c>
       <c r="C38">
-        <v>66.51805450179231</v>
+        <v>65.10365997002414</v>
       </c>
       <c r="D38">
-        <v>73.61805450179232</v>
+        <v>73.35365997002414</v>
       </c>
       <c r="E38">
-        <v>-27.4</v>
+        <v>-26.25</v>
       </c>
       <c r="F38">
-        <v>41.4</v>
+        <v>42.55</v>
       </c>
       <c r="G38">
         <v>34.3</v>
@@ -4909,28 +4909,28 @@
         <v>6.6</v>
       </c>
       <c r="M38">
-        <v>3.13812</v>
+        <v>3.22529</v>
       </c>
       <c r="N38">
-        <v>3.461879999999999</v>
+        <v>3.374709999999999</v>
       </c>
       <c r="O38">
-        <v>0.5712101999999999</v>
+        <v>0.5568271499999999</v>
       </c>
       <c r="P38">
-        <v>2.8906698</v>
+        <v>2.817882849999999</v>
       </c>
       <c r="Q38">
-        <v>8.8906698</v>
+        <v>8.81788285</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09018893825300922</v>
+        <v>0.09081442153860643</v>
       </c>
       <c r="T38">
-        <v>0.8652230276384717</v>
+        <v>0.8774148610861887</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.103170050858475</v>
+        <v>2.04632761705149</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4955,22 +4955,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08063149556932206</v>
+        <v>0.08526225065671821</v>
       </c>
       <c r="C39">
-        <v>65.10365997002414</v>
+        <v>55.34586825940391</v>
       </c>
       <c r="D39">
-        <v>73.35365997002414</v>
+        <v>64.74586825940392</v>
       </c>
       <c r="E39">
-        <v>-26.25</v>
+        <v>-25.09999999999999</v>
       </c>
       <c r="F39">
-        <v>42.55</v>
+        <v>43.7</v>
       </c>
       <c r="G39">
         <v>34.3</v>
@@ -4991,45 +4991,45 @@
         <v>6.6</v>
       </c>
       <c r="M39">
-        <v>3.22529</v>
+        <v>3.933</v>
       </c>
       <c r="N39">
-        <v>3.374709999999999</v>
+        <v>2.666999999999999</v>
       </c>
       <c r="O39">
-        <v>0.5568271499999999</v>
+        <v>0.4400549999999999</v>
       </c>
       <c r="P39">
-        <v>2.817882849999999</v>
+        <v>2.226944999999999</v>
       </c>
       <c r="Q39">
-        <v>8.81788285</v>
+        <v>8.226944999999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09081442153860643</v>
+        <v>0.0914600817043842</v>
       </c>
       <c r="T39">
-        <v>0.8774148610861887</v>
+        <v>0.889999979483832</v>
       </c>
       <c r="U39">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V39">
         <v>0.165</v>
       </c>
       <c r="W39">
-        <v>0.063293</v>
+        <v>0.07514999999999999</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y39">
-        <v>2.04632761705149</v>
+        <v>1.678108314263921</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -5037,22 +5037,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08526225065671821</v>
+        <v>0.08550591574411436</v>
       </c>
       <c r="C40">
-        <v>55.34586825940391</v>
+        <v>53.79853936389026</v>
       </c>
       <c r="D40">
-        <v>64.74586825940392</v>
+        <v>64.34853936389027</v>
       </c>
       <c r="E40">
-        <v>-25.09999999999999</v>
+        <v>-23.95</v>
       </c>
       <c r="F40">
-        <v>43.7</v>
+        <v>44.85</v>
       </c>
       <c r="G40">
         <v>34.3</v>
@@ -5073,28 +5073,28 @@
         <v>6.6</v>
       </c>
       <c r="M40">
-        <v>3.933</v>
+        <v>4.0365</v>
       </c>
       <c r="N40">
-        <v>2.666999999999999</v>
+        <v>2.563499999999999</v>
       </c>
       <c r="O40">
-        <v>0.4400549999999999</v>
+        <v>0.4229775</v>
       </c>
       <c r="P40">
-        <v>2.226944999999999</v>
+        <v>2.140522499999999</v>
       </c>
       <c r="Q40">
-        <v>8.226944999999999</v>
+        <v>8.140522499999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.0914600817043842</v>
+        <v>0.09212691105592517</v>
       </c>
       <c r="T40">
-        <v>0.889999979483832</v>
+        <v>0.9029977247141849</v>
       </c>
       <c r="U40">
         <v>0.09</v>
@@ -5111,7 +5111,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>1.678108314263921</v>
+        <v>1.635079895949461</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -5119,22 +5119,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08550591574411436</v>
+        <v>0.08574958083151051</v>
       </c>
       <c r="C41">
-        <v>53.79853936389026</v>
+        <v>52.25605733675596</v>
       </c>
       <c r="D41">
-        <v>64.34853936389027</v>
+        <v>63.95605733675595</v>
       </c>
       <c r="E41">
-        <v>-23.95</v>
+        <v>-22.8</v>
       </c>
       <c r="F41">
-        <v>44.85</v>
+        <v>46</v>
       </c>
       <c r="G41">
         <v>34.3</v>
@@ -5155,28 +5155,28 @@
         <v>6.6</v>
       </c>
       <c r="M41">
-        <v>4.0365</v>
+        <v>4.14</v>
       </c>
       <c r="N41">
-        <v>2.563499999999999</v>
+        <v>2.46</v>
       </c>
       <c r="O41">
-        <v>0.4229775</v>
+        <v>0.4059</v>
       </c>
       <c r="P41">
-        <v>2.140522499999999</v>
+        <v>2.0541</v>
       </c>
       <c r="Q41">
-        <v>8.140522499999999</v>
+        <v>8.0541</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09212691105592517</v>
+        <v>0.09281596805251752</v>
       </c>
       <c r="T41">
-        <v>0.9029977247141849</v>
+        <v>0.916428728118883</v>
       </c>
       <c r="U41">
         <v>0.09</v>
@@ -5193,7 +5193,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>1.635079895949461</v>
+        <v>1.594202898550725</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08574958083151051</v>
+        <v>0.08599324591890667</v>
       </c>
       <c r="C42">
-        <v>52.25605733675596</v>
+        <v>50.71833402792151</v>
       </c>
       <c r="D42">
-        <v>63.95605733675595</v>
+        <v>63.56833402792152</v>
       </c>
       <c r="E42">
-        <v>-22.8</v>
+        <v>-21.64999999999999</v>
       </c>
       <c r="F42">
-        <v>46</v>
+        <v>47.15000000000001</v>
       </c>
       <c r="G42">
         <v>34.3</v>
@@ -5237,28 +5237,28 @@
         <v>6.6</v>
       </c>
       <c r="M42">
-        <v>4.14</v>
+        <v>4.2435</v>
       </c>
       <c r="N42">
-        <v>2.46</v>
+        <v>2.3565</v>
       </c>
       <c r="O42">
-        <v>0.4059</v>
+        <v>0.3888225</v>
       </c>
       <c r="P42">
-        <v>2.0541</v>
+        <v>1.9676775</v>
       </c>
       <c r="Q42">
-        <v>8.0541</v>
+        <v>7.9676775</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09281596805251752</v>
+        <v>0.09352838291340113</v>
       </c>
       <c r="T42">
-        <v>0.916428728118883</v>
+        <v>0.9303150197745879</v>
       </c>
       <c r="U42">
         <v>0.09</v>
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>1.594202898550725</v>
+        <v>1.555319901025097</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5283,22 +5283,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08599324591890667</v>
+        <v>0.08623691100630282</v>
       </c>
       <c r="C43">
-        <v>50.71833402792151</v>
+        <v>49.18528341200956</v>
       </c>
       <c r="D43">
-        <v>63.56833402792152</v>
+        <v>63.18528341200957</v>
       </c>
       <c r="E43">
-        <v>-21.64999999999999</v>
+        <v>-20.49999999999999</v>
       </c>
       <c r="F43">
-        <v>47.15000000000001</v>
+        <v>48.3</v>
       </c>
       <c r="G43">
         <v>34.3</v>
@@ -5319,28 +5319,28 @@
         <v>6.6</v>
       </c>
       <c r="M43">
-        <v>4.2435</v>
+        <v>4.347</v>
       </c>
       <c r="N43">
-        <v>2.3565</v>
+        <v>2.252999999999999</v>
       </c>
       <c r="O43">
-        <v>0.3888225</v>
+        <v>0.3717449999999999</v>
       </c>
       <c r="P43">
-        <v>1.9676775</v>
+        <v>1.881254999999999</v>
       </c>
       <c r="Q43">
-        <v>7.9676775</v>
+        <v>7.881254999999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09352838291340113</v>
+        <v>0.09426536380397038</v>
       </c>
       <c r="T43">
-        <v>0.9303150197745879</v>
+        <v>0.9446801490735928</v>
       </c>
       <c r="U43">
         <v>0.09</v>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.555319901025097</v>
+        <v>1.518288474810214</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5365,22 +5365,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08623691100630282</v>
+        <v>0.108015121494026</v>
       </c>
       <c r="C44">
-        <v>49.18528341200957</v>
+        <v>25.91747075121904</v>
       </c>
       <c r="D44">
-        <v>63.18528341200957</v>
+        <v>41.06747075121904</v>
       </c>
       <c r="E44">
-        <v>-20.5</v>
+        <v>-19.35</v>
       </c>
       <c r="F44">
-        <v>48.3</v>
+        <v>49.45</v>
       </c>
       <c r="G44">
         <v>34.3</v>
@@ -5401,45 +5401,45 @@
         <v>6.6</v>
       </c>
       <c r="M44">
-        <v>4.347</v>
+        <v>7.25926</v>
       </c>
       <c r="N44">
-        <v>2.253</v>
+        <v>-0.6592600000000006</v>
       </c>
       <c r="O44">
-        <v>0.371745</v>
+        <v>-0.1087779000000001</v>
       </c>
       <c r="P44">
-        <v>1.881255</v>
+        <v>-0.5504821000000005</v>
       </c>
       <c r="Q44">
-        <v>7.881255</v>
+        <v>5.449517899999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09426536380397038</v>
+        <v>0.09536962580950407</v>
       </c>
       <c r="T44">
-        <v>0.9446801490735927</v>
+        <v>0.9662042709232345</v>
       </c>
       <c r="U44">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V44">
-        <v>0.165</v>
+        <v>0.1500152908147663</v>
       </c>
       <c r="W44">
-        <v>0.07514999999999999</v>
+        <v>0.1247777553083923</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y44">
-        <v>1.518288474810214</v>
+        <v>0.9091835806955529</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5447,22 +5447,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.108015121494026</v>
+        <v>0.109025121494026</v>
       </c>
       <c r="C45">
-        <v>25.91747075121904</v>
+        <v>24.11143175155257</v>
       </c>
       <c r="D45">
-        <v>41.06747075121904</v>
+        <v>40.41143175155257</v>
       </c>
       <c r="E45">
-        <v>-19.35</v>
+        <v>-18.2</v>
       </c>
       <c r="F45">
-        <v>49.45</v>
+        <v>50.6</v>
       </c>
       <c r="G45">
         <v>34.3</v>
@@ -5483,37 +5483,37 @@
         <v>6.6</v>
       </c>
       <c r="M45">
-        <v>7.25926</v>
+        <v>7.428080000000001</v>
       </c>
       <c r="N45">
-        <v>-0.6592600000000006</v>
+        <v>-0.8280800000000017</v>
       </c>
       <c r="O45">
-        <v>-0.1087779000000001</v>
+        <v>-0.1366332000000003</v>
       </c>
       <c r="P45">
-        <v>-0.5504821000000005</v>
+        <v>-0.6914468000000014</v>
       </c>
       <c r="Q45">
-        <v>5.449517899999999</v>
+        <v>5.308553199999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09536962580950407</v>
+        <v>0.0962547976989595</v>
       </c>
       <c r="T45">
-        <v>0.9662042709232345</v>
+        <v>0.9834579186182923</v>
       </c>
       <c r="U45">
         <v>0.1468</v>
       </c>
       <c r="V45">
-        <v>0.1500152908147663</v>
+        <v>0.1466058523871579</v>
       </c>
       <c r="W45">
-        <v>0.1247777553083923</v>
+        <v>0.1252782608695652</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.9091835806955529</v>
+        <v>0.8885203174979266</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5529,22 +5529,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.109025121494026</v>
+        <v>0.110035121494026</v>
       </c>
       <c r="C46">
-        <v>24.11143175155257</v>
+        <v>22.32602319125485</v>
       </c>
       <c r="D46">
-        <v>40.41143175155257</v>
+        <v>39.77602319125486</v>
       </c>
       <c r="E46">
-        <v>-18.2</v>
+        <v>-17.05</v>
       </c>
       <c r="F46">
-        <v>50.6</v>
+        <v>51.75</v>
       </c>
       <c r="G46">
         <v>34.3</v>
@@ -5565,37 +5565,37 @@
         <v>6.6</v>
       </c>
       <c r="M46">
-        <v>7.428080000000001</v>
+        <v>7.596900000000001</v>
       </c>
       <c r="N46">
-        <v>-0.8280800000000017</v>
+        <v>-0.996900000000001</v>
       </c>
       <c r="O46">
-        <v>-0.1366332000000003</v>
+        <v>-0.1644885000000002</v>
       </c>
       <c r="P46">
-        <v>-0.6914468000000014</v>
+        <v>-0.8324115000000009</v>
       </c>
       <c r="Q46">
-        <v>5.308553199999999</v>
+        <v>5.167588499999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.0962547976989595</v>
+        <v>0.09717215765712239</v>
       </c>
       <c r="T46">
-        <v>0.9834579186182923</v>
+        <v>1.001338971684079</v>
       </c>
       <c r="U46">
         <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.1466058523871579</v>
+        <v>0.1433479445563322</v>
       </c>
       <c r="W46">
-        <v>0.1252782608695652</v>
+        <v>0.1257565217391305</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.8885203174979266</v>
+        <v>0.8687754215535283</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5611,22 +5611,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.110035121494026</v>
+        <v>0.111045121494026</v>
       </c>
       <c r="C47">
-        <v>22.32602319125485</v>
+        <v>20.56028698748602</v>
       </c>
       <c r="D47">
-        <v>39.77602319125486</v>
+        <v>39.16028698748603</v>
       </c>
       <c r="E47">
-        <v>-17.05</v>
+        <v>-15.89999999999999</v>
       </c>
       <c r="F47">
-        <v>51.75</v>
+        <v>52.90000000000001</v>
       </c>
       <c r="G47">
         <v>34.3</v>
@@ -5647,37 +5647,37 @@
         <v>6.6</v>
       </c>
       <c r="M47">
-        <v>7.596900000000001</v>
+        <v>7.765720000000002</v>
       </c>
       <c r="N47">
-        <v>-0.996900000000001</v>
+        <v>-1.165720000000002</v>
       </c>
       <c r="O47">
-        <v>-0.1644885000000002</v>
+        <v>-0.1923438000000003</v>
       </c>
       <c r="P47">
-        <v>-0.8324115000000009</v>
+        <v>-0.9733762000000017</v>
       </c>
       <c r="Q47">
-        <v>5.167588499999999</v>
+        <v>5.026623799999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09717215765712239</v>
+        <v>0.09812349391003208</v>
       </c>
       <c r="T47">
-        <v>1.001338971684079</v>
+        <v>1.019882285974525</v>
       </c>
       <c r="U47">
         <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.1433479445563322</v>
+        <v>0.1402316848920641</v>
       </c>
       <c r="W47">
-        <v>0.1257565217391305</v>
+        <v>0.126213988657845</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5685,7 +5685,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.8687754215535283</v>
+        <v>0.8498889993458427</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5693,22 +5693,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.111045121494026</v>
+        <v>0.112055121494026</v>
       </c>
       <c r="C48">
-        <v>20.56028698748602</v>
+        <v>18.81332347786621</v>
       </c>
       <c r="D48">
-        <v>39.16028698748603</v>
+        <v>38.56332347786622</v>
       </c>
       <c r="E48">
-        <v>-15.89999999999999</v>
+        <v>-14.74999999999999</v>
       </c>
       <c r="F48">
-        <v>52.90000000000001</v>
+        <v>54.05</v>
       </c>
       <c r="G48">
         <v>34.3</v>
@@ -5729,37 +5729,37 @@
         <v>6.6</v>
       </c>
       <c r="M48">
-        <v>7.765720000000002</v>
+        <v>7.934540000000001</v>
       </c>
       <c r="N48">
-        <v>-1.165720000000002</v>
+        <v>-1.334540000000001</v>
       </c>
       <c r="O48">
-        <v>-0.1923438000000003</v>
+        <v>-0.2201991000000002</v>
       </c>
       <c r="P48">
-        <v>-0.9733762000000017</v>
+        <v>-1.114340900000001</v>
       </c>
       <c r="Q48">
-        <v>5.026623799999999</v>
+        <v>4.885659099999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09812349391003208</v>
+        <v>0.09911072964418363</v>
       </c>
       <c r="T48">
-        <v>1.019882285974525</v>
+        <v>1.039125347974045</v>
       </c>
       <c r="U48">
         <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.1402316848920641</v>
+        <v>0.1372480320220202</v>
       </c>
       <c r="W48">
-        <v>0.126213988657845</v>
+        <v>0.1266519888991675</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.8498889993458427</v>
+        <v>0.83180625467891</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5775,22 +5775,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.112055121494026</v>
+        <v>0.113065121494026</v>
       </c>
       <c r="C49">
-        <v>18.81332347786621</v>
+        <v>17.08428703449779</v>
       </c>
       <c r="D49">
-        <v>38.56332347786622</v>
+        <v>37.9842870344978</v>
       </c>
       <c r="E49">
-        <v>-14.74999999999999</v>
+        <v>-13.59999999999999</v>
       </c>
       <c r="F49">
-        <v>54.05</v>
+        <v>55.2</v>
       </c>
       <c r="G49">
         <v>34.3</v>
@@ -5811,37 +5811,37 @@
         <v>6.6</v>
       </c>
       <c r="M49">
-        <v>7.934540000000001</v>
+        <v>8.10336</v>
       </c>
       <c r="N49">
-        <v>-1.334540000000001</v>
+        <v>-1.503360000000001</v>
       </c>
       <c r="O49">
-        <v>-0.2201991000000002</v>
+        <v>-0.2480544000000001</v>
       </c>
       <c r="P49">
-        <v>-1.114340900000001</v>
+        <v>-1.255305600000001</v>
       </c>
       <c r="Q49">
-        <v>4.885659099999999</v>
+        <v>4.744694399999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09911072964418363</v>
+        <v>0.1001359359834949</v>
       </c>
       <c r="T49">
-        <v>1.039125347974045</v>
+        <v>1.059108527742776</v>
       </c>
       <c r="U49">
         <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.1372480320220202</v>
+        <v>0.1343886980215614</v>
       </c>
       <c r="W49">
-        <v>0.1266519888991675</v>
+        <v>0.1270717391304348</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.83180625467891</v>
+        <v>0.8144769577064328</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5857,22 +5857,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.113065121494026</v>
+        <v>0.1410590641917817</v>
       </c>
       <c r="C50">
-        <v>17.0842870344978</v>
+        <v>4.771780204511835</v>
       </c>
       <c r="D50">
-        <v>37.9842870344978</v>
+        <v>26.82178020451184</v>
       </c>
       <c r="E50">
-        <v>-13.6</v>
+        <v>-12.45</v>
       </c>
       <c r="F50">
-        <v>55.2</v>
+        <v>56.35</v>
       </c>
       <c r="G50">
         <v>34.3</v>
@@ -5893,45 +5893,45 @@
         <v>6.6</v>
       </c>
       <c r="M50">
-        <v>8.10336</v>
+        <v>11.31508</v>
       </c>
       <c r="N50">
-        <v>-1.503360000000001</v>
+        <v>-4.71508</v>
       </c>
       <c r="O50">
-        <v>-0.2480544000000001</v>
+        <v>-0.7779882000000001</v>
       </c>
       <c r="P50">
-        <v>-1.255305600000001</v>
+        <v>-3.9370918</v>
       </c>
       <c r="Q50">
-        <v>4.744694399999999</v>
+        <v>2.0629082</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1001359359834949</v>
+        <v>0.1022286851160255</v>
       </c>
       <c r="T50">
-        <v>1.059108527742776</v>
+        <v>1.09990010356771</v>
       </c>
       <c r="U50">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.1343886980215614</v>
+        <v>0.0962432435298734</v>
       </c>
       <c r="W50">
-        <v>0.1270717391304348</v>
+        <v>0.1814743566992014</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y50">
-        <v>0.8144769577064328</v>
+        <v>0.5832923850295357</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5939,22 +5939,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1410590641917817</v>
+        <v>0.1426090641917817</v>
       </c>
       <c r="C51">
-        <v>4.771780204511835</v>
+        <v>3.192339431955304</v>
       </c>
       <c r="D51">
-        <v>26.82178020451184</v>
+        <v>26.3923394319553</v>
       </c>
       <c r="E51">
-        <v>-12.45</v>
+        <v>-11.3</v>
       </c>
       <c r="F51">
-        <v>56.35</v>
+        <v>57.5</v>
       </c>
       <c r="G51">
         <v>34.3</v>
@@ -5975,37 +5975,37 @@
         <v>6.6</v>
       </c>
       <c r="M51">
-        <v>11.31508</v>
+        <v>11.546</v>
       </c>
       <c r="N51">
-        <v>-4.71508</v>
+        <v>-4.946000000000002</v>
       </c>
       <c r="O51">
-        <v>-0.7779882000000001</v>
+        <v>-0.8160900000000003</v>
       </c>
       <c r="P51">
-        <v>-3.9370918</v>
+        <v>-4.129910000000002</v>
       </c>
       <c r="Q51">
-        <v>2.0629082</v>
+        <v>1.870089999999998</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1022286851160255</v>
+        <v>0.103357258818346</v>
       </c>
       <c r="T51">
-        <v>1.09990010356771</v>
+        <v>1.121898105639065</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.0962432435298734</v>
+        <v>0.09431837865927592</v>
       </c>
       <c r="W51">
-        <v>0.1814743566992014</v>
+        <v>0.1818608695652174</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5832923850295357</v>
+        <v>0.5716265373289451</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -6021,22 +6021,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1426090641917817</v>
+        <v>0.1441590641917817</v>
       </c>
       <c r="C52">
-        <v>3.192339431955304</v>
+        <v>1.626433420082641</v>
       </c>
       <c r="D52">
-        <v>26.3923394319553</v>
+        <v>25.97643342008264</v>
       </c>
       <c r="E52">
-        <v>-11.3</v>
+        <v>-10.15</v>
       </c>
       <c r="F52">
-        <v>57.5</v>
+        <v>58.65</v>
       </c>
       <c r="G52">
         <v>34.3</v>
@@ -6057,37 +6057,37 @@
         <v>6.6</v>
       </c>
       <c r="M52">
-        <v>11.546</v>
+        <v>11.77692</v>
       </c>
       <c r="N52">
-        <v>-4.946000000000002</v>
+        <v>-5.176920000000001</v>
       </c>
       <c r="O52">
-        <v>-0.8160900000000003</v>
+        <v>-0.8541918000000002</v>
       </c>
       <c r="P52">
-        <v>-4.129910000000002</v>
+        <v>-4.3227282</v>
       </c>
       <c r="Q52">
-        <v>1.870089999999998</v>
+        <v>1.6772718</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.103357258818346</v>
+        <v>0.1045318967534143</v>
       </c>
       <c r="T52">
-        <v>1.121898105639065</v>
+        <v>1.144793985345984</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.09431837865927592</v>
+        <v>0.09246899868556463</v>
       </c>
       <c r="W52">
-        <v>0.1818608695652174</v>
+        <v>0.1822322250639386</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.5716265373289451</v>
+        <v>0.560418173851907</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -6103,22 +6103,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1441590641917817</v>
+        <v>0.1457090641917817</v>
       </c>
       <c r="C53">
-        <v>1.626433420082641</v>
+        <v>0.07343222968173535</v>
       </c>
       <c r="D53">
-        <v>25.97643342008264</v>
+        <v>25.57343222968174</v>
       </c>
       <c r="E53">
-        <v>-10.15</v>
+        <v>-8.999999999999993</v>
       </c>
       <c r="F53">
-        <v>58.65</v>
+        <v>59.8</v>
       </c>
       <c r="G53">
         <v>34.3</v>
@@ -6139,37 +6139,37 @@
         <v>6.6</v>
       </c>
       <c r="M53">
-        <v>11.77692</v>
+        <v>12.00784</v>
       </c>
       <c r="N53">
-        <v>-5.176920000000001</v>
+        <v>-5.407840000000002</v>
       </c>
       <c r="O53">
-        <v>-0.8541918000000002</v>
+        <v>-0.8922936000000004</v>
       </c>
       <c r="P53">
-        <v>-4.3227282</v>
+        <v>-4.515546400000002</v>
       </c>
       <c r="Q53">
-        <v>1.6772718</v>
+        <v>1.484453599999998</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1045318967534143</v>
+        <v>0.1057554779357771</v>
       </c>
       <c r="T53">
-        <v>1.144793985345984</v>
+        <v>1.168643860040692</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.09246899868556463</v>
+        <v>0.09069074871084223</v>
       </c>
       <c r="W53">
-        <v>0.1822322250639386</v>
+        <v>0.1825892976588629</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.560418173851907</v>
+        <v>0.5496409012778317</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -6185,22 +6185,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1457090641917817</v>
+        <v>0.1472590641917817</v>
       </c>
       <c r="C54">
-        <v>0.07343222968173535</v>
+        <v>-1.467255583888864</v>
       </c>
       <c r="D54">
-        <v>25.57343222968174</v>
+        <v>25.18274441611114</v>
       </c>
       <c r="E54">
-        <v>-8.999999999999993</v>
+        <v>-7.849999999999994</v>
       </c>
       <c r="F54">
-        <v>59.8</v>
+        <v>60.95</v>
       </c>
       <c r="G54">
         <v>34.3</v>
@@ -6221,37 +6221,37 @@
         <v>6.6</v>
       </c>
       <c r="M54">
-        <v>12.00784</v>
+        <v>12.23876</v>
       </c>
       <c r="N54">
-        <v>-5.407840000000002</v>
+        <v>-5.638760000000001</v>
       </c>
       <c r="O54">
-        <v>-0.8922936000000004</v>
+        <v>-0.9303954000000003</v>
       </c>
       <c r="P54">
-        <v>-4.515546400000002</v>
+        <v>-4.708364600000001</v>
       </c>
       <c r="Q54">
-        <v>1.484453599999998</v>
+        <v>1.291635399999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1057554779357771</v>
+        <v>0.1070311264024957</v>
       </c>
       <c r="T54">
-        <v>1.168643860040692</v>
+        <v>1.193508623020282</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.09069074871084223</v>
+        <v>0.08897960250875088</v>
       </c>
       <c r="W54">
-        <v>0.1825892976588629</v>
+        <v>0.1829328958162428</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5496409012778317</v>
+        <v>0.5392703182348537</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1472590641917817</v>
+        <v>0.1488090641917817</v>
       </c>
       <c r="C55">
-        <v>-1.467255583888864</v>
+        <v>-2.996185866881248</v>
       </c>
       <c r="D55">
-        <v>25.18274441611114</v>
+        <v>24.80381413311876</v>
       </c>
       <c r="E55">
-        <v>-7.849999999999994</v>
+        <v>-6.699999999999996</v>
       </c>
       <c r="F55">
-        <v>60.95</v>
+        <v>62.1</v>
       </c>
       <c r="G55">
         <v>34.3</v>
@@ -6303,37 +6303,37 @@
         <v>6.6</v>
       </c>
       <c r="M55">
-        <v>12.23876</v>
+        <v>12.46968</v>
       </c>
       <c r="N55">
-        <v>-5.638760000000001</v>
+        <v>-5.869680000000001</v>
       </c>
       <c r="O55">
-        <v>-0.9303954000000003</v>
+        <v>-0.9684972000000002</v>
       </c>
       <c r="P55">
-        <v>-4.708364600000001</v>
+        <v>-4.901182800000001</v>
       </c>
       <c r="Q55">
-        <v>1.291635399999999</v>
+        <v>1.098817199999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1070311264024957</v>
+        <v>0.1083622378460282</v>
       </c>
       <c r="T55">
-        <v>1.193508623020282</v>
+        <v>1.219454462651157</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.08897960250875088</v>
+        <v>0.08733183209192216</v>
       </c>
       <c r="W55">
-        <v>0.1829328958162428</v>
+        <v>0.183263768115942</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5392703182348537</v>
+        <v>0.5292838308601343</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6349,22 +6349,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1488090641917817</v>
+        <v>0.1503590641917817</v>
       </c>
       <c r="C56">
-        <v>-2.996185866881248</v>
+        <v>-4.513881505738702</v>
       </c>
       <c r="D56">
-        <v>24.80381413311876</v>
+        <v>24.4361184942613</v>
       </c>
       <c r="E56">
-        <v>-6.699999999999996</v>
+        <v>-5.54999999999999</v>
       </c>
       <c r="F56">
-        <v>62.1</v>
+        <v>63.25000000000001</v>
       </c>
       <c r="G56">
         <v>34.3</v>
@@ -6385,37 +6385,37 @@
         <v>6.6</v>
       </c>
       <c r="M56">
-        <v>12.46968</v>
+        <v>12.7006</v>
       </c>
       <c r="N56">
-        <v>-5.869680000000001</v>
+        <v>-6.100600000000002</v>
       </c>
       <c r="O56">
-        <v>-0.9684972000000002</v>
+        <v>-1.006599</v>
       </c>
       <c r="P56">
-        <v>-4.901182800000001</v>
+        <v>-5.094001000000001</v>
       </c>
       <c r="Q56">
-        <v>1.098817199999999</v>
+        <v>0.9059989999999987</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1083622378460282</v>
+        <v>0.1097525097981622</v>
       </c>
       <c r="T56">
-        <v>1.219454462651157</v>
+        <v>1.246553450710072</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.08733183209192216</v>
+        <v>0.08574398059934175</v>
       </c>
       <c r="W56">
-        <v>0.183263768115942</v>
+        <v>0.1835826086956522</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5292838308601343</v>
+        <v>0.5196604884808591</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6431,22 +6431,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1503590641917817</v>
+        <v>0.1519090641917817</v>
       </c>
       <c r="C57">
-        <v>-4.513881505738702</v>
+        <v>-6.020834834416142</v>
       </c>
       <c r="D57">
-        <v>24.4361184942613</v>
+        <v>24.07916516558387</v>
       </c>
       <c r="E57">
-        <v>-5.54999999999999</v>
+        <v>-4.399999999999991</v>
       </c>
       <c r="F57">
-        <v>63.25000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="G57">
         <v>34.3</v>
@@ -6467,37 +6467,37 @@
         <v>6.6</v>
       </c>
       <c r="M57">
-        <v>12.7006</v>
+        <v>12.93152</v>
       </c>
       <c r="N57">
-        <v>-6.100600000000002</v>
+        <v>-6.331520000000001</v>
       </c>
       <c r="O57">
-        <v>-1.006599</v>
+        <v>-1.0447008</v>
       </c>
       <c r="P57">
-        <v>-5.094001000000001</v>
+        <v>-5.286819200000001</v>
       </c>
       <c r="Q57">
-        <v>0.9059989999999987</v>
+        <v>0.7131807999999991</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1097525097981622</v>
+        <v>0.1112059759299386</v>
       </c>
       <c r="T57">
-        <v>1.246553450710072</v>
+        <v>1.274884210953483</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.08574398059934175</v>
+        <v>0.08421283808863923</v>
       </c>
       <c r="W57">
-        <v>0.1835826086956522</v>
+        <v>0.1838900621118013</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5196604884808591</v>
+        <v>0.5103808369008438</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6513,22 +6513,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1519090641917817</v>
+        <v>0.1534590641917817</v>
       </c>
       <c r="C58">
-        <v>-6.020834834416142</v>
+        <v>-7.517509833747084</v>
       </c>
       <c r="D58">
-        <v>24.07916516558387</v>
+        <v>23.73249016625293</v>
       </c>
       <c r="E58">
-        <v>-4.399999999999991</v>
+        <v>-3.249999999999986</v>
       </c>
       <c r="F58">
-        <v>64.40000000000001</v>
+        <v>65.55000000000001</v>
       </c>
       <c r="G58">
         <v>34.3</v>
@@ -6549,37 +6549,37 @@
         <v>6.6</v>
       </c>
       <c r="M58">
-        <v>12.93152</v>
+        <v>13.16244</v>
       </c>
       <c r="N58">
-        <v>-6.331520000000001</v>
+        <v>-6.562440000000002</v>
       </c>
       <c r="O58">
-        <v>-1.0447008</v>
+        <v>-1.0828026</v>
       </c>
       <c r="P58">
-        <v>-5.286819200000001</v>
+        <v>-5.479637400000001</v>
       </c>
       <c r="Q58">
-        <v>0.7131807999999991</v>
+        <v>0.5203625999999986</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1112059759299386</v>
+        <v>0.1127270451376116</v>
       </c>
       <c r="T58">
-        <v>1.274884210953483</v>
+        <v>1.304532680975657</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.08421283808863923</v>
+        <v>0.08273541987655783</v>
       </c>
       <c r="W58">
-        <v>0.1838900621118013</v>
+        <v>0.1841867276887872</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5103808369008438</v>
+        <v>0.5014267871306535</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6595,22 +6595,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1534590641917817</v>
+        <v>0.1755204813988521</v>
       </c>
       <c r="C59">
-        <v>-7.517509833747084</v>
+        <v>-12.70366789664057</v>
       </c>
       <c r="D59">
-        <v>23.73249016625293</v>
+        <v>19.69633210335944</v>
       </c>
       <c r="E59">
-        <v>-3.249999999999986</v>
+        <v>-2.099999999999994</v>
       </c>
       <c r="F59">
-        <v>65.55000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="G59">
         <v>34.3</v>
@@ -6631,45 +6631,45 @@
         <v>6.6</v>
       </c>
       <c r="M59">
-        <v>13.16244</v>
+        <v>15.72786</v>
       </c>
       <c r="N59">
-        <v>-6.562440000000002</v>
+        <v>-9.127860000000002</v>
       </c>
       <c r="O59">
-        <v>-1.0828026</v>
+        <v>-1.5060969</v>
       </c>
       <c r="P59">
-        <v>-5.479637400000001</v>
+        <v>-7.621763100000002</v>
       </c>
       <c r="Q59">
-        <v>0.5203625999999986</v>
+        <v>-1.621763100000002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1127270451376116</v>
+        <v>0.1148239205148652</v>
       </c>
       <c r="T59">
-        <v>1.304532680975657</v>
+        <v>1.345404684990416</v>
       </c>
       <c r="U59">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.08273541987655783</v>
+        <v>0.06924018906577245</v>
       </c>
       <c r="W59">
-        <v>0.1841867276887872</v>
+        <v>0.2194731634182909</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y59">
-        <v>0.5014267871306535</v>
+        <v>0.4196375094895299</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6677,22 +6677,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1755204813988521</v>
+        <v>0.1774204813988521</v>
       </c>
       <c r="C60">
-        <v>-12.70366789664054</v>
+        <v>-14.1379931824825</v>
       </c>
       <c r="D60">
-        <v>19.69633210335945</v>
+        <v>19.4120068175175</v>
       </c>
       <c r="E60">
-        <v>-2.100000000000009</v>
+        <v>-0.9500000000000028</v>
       </c>
       <c r="F60">
-        <v>66.69999999999999</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="G60">
         <v>34.3</v>
@@ -6713,37 +6713,37 @@
         <v>6.6</v>
       </c>
       <c r="M60">
-        <v>15.72786</v>
+        <v>15.99903</v>
       </c>
       <c r="N60">
-        <v>-9.127859999999998</v>
+        <v>-9.39903</v>
       </c>
       <c r="O60">
-        <v>-1.5060969</v>
+        <v>-1.55083995</v>
       </c>
       <c r="P60">
-        <v>-7.621763099999999</v>
+        <v>-7.848190049999999</v>
       </c>
       <c r="Q60">
-        <v>-1.621763099999999</v>
+        <v>-1.848190049999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1148239205148652</v>
+        <v>0.1165074307713253</v>
       </c>
       <c r="T60">
-        <v>1.345404684990416</v>
+        <v>1.378219433404816</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.06924018906577246</v>
+        <v>0.06806662653923394</v>
       </c>
       <c r="W60">
-        <v>0.2194731634182909</v>
+        <v>0.2197498894620487</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.41963750948953</v>
+        <v>0.4125250093286905</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6759,22 +6759,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1774204813988521</v>
+        <v>0.1793204813988521</v>
       </c>
       <c r="C61">
-        <v>-14.1379931824825</v>
+        <v>-15.56422655557158</v>
       </c>
       <c r="D61">
-        <v>19.4120068175175</v>
+        <v>19.13577344442842</v>
       </c>
       <c r="E61">
-        <v>-0.9500000000000028</v>
+        <v>0.2000000000000028</v>
       </c>
       <c r="F61">
-        <v>67.84999999999999</v>
+        <v>69</v>
       </c>
       <c r="G61">
         <v>34.3</v>
@@ -6795,37 +6795,37 @@
         <v>6.6</v>
       </c>
       <c r="M61">
-        <v>15.99903</v>
+        <v>16.2702</v>
       </c>
       <c r="N61">
-        <v>-9.39903</v>
+        <v>-9.670199999999999</v>
       </c>
       <c r="O61">
-        <v>-1.55083995</v>
+        <v>-1.595583</v>
       </c>
       <c r="P61">
-        <v>-7.848190049999999</v>
+        <v>-8.074617</v>
       </c>
       <c r="Q61">
-        <v>-1.848190049999999</v>
+        <v>-2.074617</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1165074307713253</v>
+        <v>0.1182751165406085</v>
       </c>
       <c r="T61">
-        <v>1.378219433404816</v>
+        <v>1.412674919239937</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.06806662653923394</v>
+        <v>0.06693218276358004</v>
       </c>
       <c r="W61">
-        <v>0.2197498894620487</v>
+        <v>0.2200173913043478</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.4125250093286905</v>
+        <v>0.4056495925065458</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6841,22 +6841,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1793204813988521</v>
+        <v>0.1812204813988521</v>
       </c>
       <c r="C62">
-        <v>-15.56422655557158</v>
+        <v>-16.98270861359447</v>
       </c>
       <c r="D62">
-        <v>19.13577344442842</v>
+        <v>18.86729138640553</v>
       </c>
       <c r="E62">
-        <v>0.2000000000000028</v>
+        <v>1.349999999999994</v>
       </c>
       <c r="F62">
-        <v>69</v>
+        <v>70.14999999999999</v>
       </c>
       <c r="G62">
         <v>34.3</v>
@@ -6877,37 +6877,37 @@
         <v>6.6</v>
       </c>
       <c r="M62">
-        <v>16.2702</v>
+        <v>16.54137</v>
       </c>
       <c r="N62">
-        <v>-9.670199999999999</v>
+        <v>-9.941369999999997</v>
       </c>
       <c r="O62">
-        <v>-1.595583</v>
+        <v>-1.64032605</v>
       </c>
       <c r="P62">
-        <v>-8.074617</v>
+        <v>-8.301043949999997</v>
       </c>
       <c r="Q62">
-        <v>-2.074617</v>
+        <v>-2.301043949999997</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1182751165406085</v>
+        <v>0.1201334528621625</v>
       </c>
       <c r="T62">
-        <v>1.412674919239937</v>
+        <v>1.448897353066602</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.06693218276358004</v>
+        <v>0.06583493386581644</v>
       </c>
       <c r="W62">
-        <v>0.2200173913043478</v>
+        <v>0.2202761225944405</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.4056495925065458</v>
+        <v>0.3989995991867663</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6923,22 +6923,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1812204813988521</v>
+        <v>0.1831204813988521</v>
       </c>
       <c r="C63">
-        <v>-16.98270861359447</v>
+        <v>-18.39376110386392</v>
       </c>
       <c r="D63">
-        <v>18.86729138640553</v>
+        <v>18.60623889613607</v>
       </c>
       <c r="E63">
-        <v>1.349999999999994</v>
+        <v>2.5</v>
       </c>
       <c r="F63">
-        <v>70.14999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="G63">
         <v>34.3</v>
@@ -6959,37 +6959,37 @@
         <v>6.6</v>
       </c>
       <c r="M63">
-        <v>16.54137</v>
+        <v>16.81254</v>
       </c>
       <c r="N63">
-        <v>-9.941369999999997</v>
+        <v>-10.21254</v>
       </c>
       <c r="O63">
-        <v>-1.64032605</v>
+        <v>-1.6850691</v>
       </c>
       <c r="P63">
-        <v>-8.301043949999997</v>
+        <v>-8.527470899999999</v>
       </c>
       <c r="Q63">
-        <v>-2.301043949999997</v>
+        <v>-2.527470899999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1201334528621625</v>
+        <v>0.1220895963585352</v>
       </c>
       <c r="T63">
-        <v>1.448897353066602</v>
+        <v>1.487026230778881</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.06583493386581644</v>
+        <v>0.06477308009378714</v>
       </c>
       <c r="W63">
-        <v>0.2202761225944405</v>
+        <v>0.220526507713885</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3989995991867663</v>
+        <v>0.3925641217805281</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -7005,22 +7005,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1831204813988521</v>
+        <v>0.1850204813988521</v>
       </c>
       <c r="C64">
-        <v>-18.39376110386392</v>
+        <v>-19.7976882096134</v>
       </c>
       <c r="D64">
-        <v>18.60623889613607</v>
+        <v>18.35231179038661</v>
       </c>
       <c r="E64">
-        <v>2.5</v>
+        <v>3.650000000000006</v>
       </c>
       <c r="F64">
-        <v>71.3</v>
+        <v>72.45</v>
       </c>
       <c r="G64">
         <v>34.3</v>
@@ -7041,37 +7041,37 @@
         <v>6.6</v>
       </c>
       <c r="M64">
-        <v>16.81254</v>
+        <v>17.08371</v>
       </c>
       <c r="N64">
-        <v>-10.21254</v>
+        <v>-10.48371</v>
       </c>
       <c r="O64">
-        <v>-1.6850691</v>
+        <v>-1.72981215</v>
       </c>
       <c r="P64">
-        <v>-8.527470899999999</v>
+        <v>-8.75389785</v>
       </c>
       <c r="Q64">
-        <v>-2.527470899999999</v>
+        <v>-2.75389785</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1220895963585352</v>
+        <v>0.1241514773411983</v>
       </c>
       <c r="T64">
-        <v>1.487026230778881</v>
+        <v>1.52721612890804</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.06477308009378714</v>
+        <v>0.06374493596531432</v>
       </c>
       <c r="W64">
-        <v>0.220526507713885</v>
+        <v>0.2207689440993789</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3925641217805281</v>
+        <v>0.3863329452443293</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -7087,22 +7087,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1850204813988521</v>
+        <v>0.1869204813988521</v>
       </c>
       <c r="C65">
-        <v>-19.7976882096134</v>
+        <v>-21.19477773238213</v>
       </c>
       <c r="D65">
-        <v>18.35231179038661</v>
+        <v>18.10522226761788</v>
       </c>
       <c r="E65">
-        <v>3.650000000000006</v>
+        <v>4.800000000000011</v>
       </c>
       <c r="F65">
-        <v>72.45</v>
+        <v>73.60000000000001</v>
       </c>
       <c r="G65">
         <v>34.3</v>
@@ -7123,37 +7123,37 @@
         <v>6.6</v>
       </c>
       <c r="M65">
-        <v>17.08371</v>
+        <v>17.35488</v>
       </c>
       <c r="N65">
-        <v>-10.48371</v>
+        <v>-10.75488</v>
       </c>
       <c r="O65">
-        <v>-1.72981215</v>
+        <v>-1.7745552</v>
       </c>
       <c r="P65">
-        <v>-8.75389785</v>
+        <v>-8.980324800000002</v>
       </c>
       <c r="Q65">
-        <v>-2.75389785</v>
+        <v>-2.980324800000002</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1241514773411983</v>
+        <v>0.1263279072673427</v>
       </c>
       <c r="T65">
-        <v>1.52721612890804</v>
+        <v>1.569638799155486</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.06374493596531432</v>
+        <v>0.06274892134085629</v>
       </c>
       <c r="W65">
-        <v>0.2207689440993789</v>
+        <v>0.2210038043478261</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3863329452443293</v>
+        <v>0.3802964929748865</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -7169,22 +7169,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1869204813988521</v>
+        <v>0.1888204813988521</v>
       </c>
       <c r="C66">
-        <v>-21.19477773238213</v>
+        <v>-22.58530218015363</v>
       </c>
       <c r="D66">
-        <v>18.10522226761788</v>
+        <v>17.86469781984638</v>
       </c>
       <c r="E66">
-        <v>4.800000000000011</v>
+        <v>5.950000000000003</v>
       </c>
       <c r="F66">
-        <v>73.60000000000001</v>
+        <v>74.75</v>
       </c>
       <c r="G66">
         <v>34.3</v>
@@ -7205,37 +7205,37 @@
         <v>6.6</v>
       </c>
       <c r="M66">
-        <v>17.35488</v>
+        <v>17.62605</v>
       </c>
       <c r="N66">
-        <v>-10.75488</v>
+        <v>-11.02605</v>
       </c>
       <c r="O66">
-        <v>-1.7745552</v>
+        <v>-1.81929825</v>
       </c>
       <c r="P66">
-        <v>-8.980324800000002</v>
+        <v>-9.206751749999999</v>
       </c>
       <c r="Q66">
-        <v>-2.980324800000002</v>
+        <v>-3.206751749999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1263279072673427</v>
+        <v>0.1286287046178383</v>
       </c>
       <c r="T66">
-        <v>1.569638799155486</v>
+        <v>1.6144856219885</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.06274892134085629</v>
+        <v>0.06178355332022773</v>
       </c>
       <c r="W66">
-        <v>0.2210038043478261</v>
+        <v>0.2212314381270903</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3802964929748865</v>
+        <v>0.3744457776983499</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7251,22 +7251,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1888204813988521</v>
+        <v>0.1907204813988521</v>
       </c>
       <c r="C67">
-        <v>-22.58530218015363</v>
+        <v>-23.96951976989715</v>
       </c>
       <c r="D67">
-        <v>17.86469781984638</v>
+        <v>17.63048023010287</v>
       </c>
       <c r="E67">
-        <v>5.950000000000003</v>
+        <v>7.100000000000009</v>
       </c>
       <c r="F67">
-        <v>74.75</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="G67">
         <v>34.3</v>
@@ -7287,37 +7287,37 @@
         <v>6.6</v>
       </c>
       <c r="M67">
-        <v>17.62605</v>
+        <v>17.89722</v>
       </c>
       <c r="N67">
-        <v>-11.02605</v>
+        <v>-11.29722</v>
       </c>
       <c r="O67">
-        <v>-1.81929825</v>
+        <v>-1.8640413</v>
       </c>
       <c r="P67">
-        <v>-9.206751749999999</v>
+        <v>-9.433178700000001</v>
       </c>
       <c r="Q67">
-        <v>-3.206751749999999</v>
+        <v>-3.433178700000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1286287046178383</v>
+        <v>0.1310648429889512</v>
       </c>
       <c r="T67">
-        <v>1.6144856219885</v>
+        <v>1.661970493223455</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.06178355332022773</v>
+        <v>0.06084743887598186</v>
       </c>
       <c r="W67">
-        <v>0.2212314381270903</v>
+        <v>0.2214521739130435</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3744457776983499</v>
+        <v>0.3687723568241325</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7333,22 +7333,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1907204813988521</v>
+        <v>0.1926204813988521</v>
       </c>
       <c r="C68">
-        <v>-23.96951976989715</v>
+        <v>-25.34767535226575</v>
       </c>
       <c r="D68">
-        <v>17.63048023010287</v>
+        <v>17.40232464773426</v>
       </c>
       <c r="E68">
-        <v>7.100000000000009</v>
+        <v>8.250000000000014</v>
       </c>
       <c r="F68">
-        <v>75.90000000000001</v>
+        <v>77.05000000000001</v>
       </c>
       <c r="G68">
         <v>34.3</v>
@@ -7369,37 +7369,37 @@
         <v>6.6</v>
       </c>
       <c r="M68">
-        <v>17.89722</v>
+        <v>18.16839</v>
       </c>
       <c r="N68">
-        <v>-11.29722</v>
+        <v>-11.56839</v>
       </c>
       <c r="O68">
-        <v>-1.8640413</v>
+        <v>-1.908784350000001</v>
       </c>
       <c r="P68">
-        <v>-9.433178700000001</v>
+        <v>-9.659605650000001</v>
       </c>
       <c r="Q68">
-        <v>-3.433178700000001</v>
+        <v>-3.659605650000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1310648429889512</v>
+        <v>0.1336486261098284</v>
       </c>
       <c r="T68">
-        <v>1.661970493223455</v>
+        <v>1.712333235442348</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.06084743887598186</v>
+        <v>0.05993926814648959</v>
       </c>
       <c r="W68">
-        <v>0.2214521739130435</v>
+        <v>0.2216663205710578</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3687723568241325</v>
+        <v>0.3632682917969066</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7415,22 +7415,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1926204813988521</v>
+        <v>0.1945204813988521</v>
       </c>
       <c r="C69">
-        <v>-25.34767535226575</v>
+        <v>-26.72000126541298</v>
       </c>
       <c r="D69">
-        <v>17.40232464773426</v>
+        <v>17.17999873458702</v>
       </c>
       <c r="E69">
-        <v>8.250000000000014</v>
+        <v>9.400000000000006</v>
       </c>
       <c r="F69">
-        <v>77.05000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="G69">
         <v>34.3</v>
@@ -7451,37 +7451,37 @@
         <v>6.6</v>
       </c>
       <c r="M69">
-        <v>18.16839</v>
+        <v>18.43956</v>
       </c>
       <c r="N69">
-        <v>-11.56839</v>
+        <v>-11.83956</v>
       </c>
       <c r="O69">
-        <v>-1.908784350000001</v>
+        <v>-1.9535274</v>
       </c>
       <c r="P69">
-        <v>-9.659605650000001</v>
+        <v>-9.8860326</v>
       </c>
       <c r="Q69">
-        <v>-3.659605650000001</v>
+        <v>-3.8860326</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1336486261098284</v>
+        <v>0.1363938956757606</v>
       </c>
       <c r="T69">
-        <v>1.712333235442348</v>
+        <v>1.765843649049921</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.05993926814648959</v>
+        <v>0.05905780832080591</v>
       </c>
       <c r="W69">
-        <v>0.2216663205710578</v>
+        <v>0.221874168797954</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7489,7 +7489,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3632682917969066</v>
+        <v>0.3579261110351873</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7497,22 +7497,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1945204813988521</v>
+        <v>0.1964204813988521</v>
       </c>
       <c r="C70">
-        <v>-26.72000126541298</v>
+        <v>-28.08671812418652</v>
       </c>
       <c r="D70">
-        <v>17.17999873458702</v>
+        <v>16.96328187581349</v>
       </c>
       <c r="E70">
-        <v>9.400000000000006</v>
+        <v>10.55000000000001</v>
       </c>
       <c r="F70">
-        <v>78.2</v>
+        <v>79.35000000000001</v>
       </c>
       <c r="G70">
         <v>34.3</v>
@@ -7533,37 +7533,37 @@
         <v>6.6</v>
       </c>
       <c r="M70">
-        <v>18.43956</v>
+        <v>18.71073</v>
       </c>
       <c r="N70">
-        <v>-11.83956</v>
+        <v>-12.11073</v>
       </c>
       <c r="O70">
-        <v>-1.9535274</v>
+        <v>-1.99827045</v>
       </c>
       <c r="P70">
-        <v>-9.8860326</v>
+        <v>-10.11245955</v>
       </c>
       <c r="Q70">
-        <v>-3.8860326</v>
+        <v>-4.112459550000002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1363938956757606</v>
+        <v>0.1393162794072368</v>
       </c>
       <c r="T70">
-        <v>1.765843649049921</v>
+        <v>1.822806347406371</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.05905780832080591</v>
+        <v>0.05820189805528699</v>
       </c>
       <c r="W70">
-        <v>0.221874168797954</v>
+        <v>0.2220759924385634</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7571,7 +7571,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3579261110351873</v>
+        <v>0.3527387760926484</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7579,22 +7579,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1964204813988521</v>
+        <v>0.1983204813988521</v>
       </c>
       <c r="C71">
-        <v>-28.08671812418652</v>
+        <v>-29.44803555033442</v>
       </c>
       <c r="D71">
-        <v>16.96328187581349</v>
+        <v>16.75196444966559</v>
       </c>
       <c r="E71">
-        <v>10.55000000000001</v>
+        <v>11.70000000000002</v>
       </c>
       <c r="F71">
-        <v>79.35000000000001</v>
+        <v>80.50000000000001</v>
       </c>
       <c r="G71">
         <v>34.3</v>
@@ -7615,37 +7615,37 @@
         <v>6.6</v>
       </c>
       <c r="M71">
-        <v>18.71073</v>
+        <v>18.9819</v>
       </c>
       <c r="N71">
-        <v>-12.11073</v>
+        <v>-12.3819</v>
       </c>
       <c r="O71">
-        <v>-1.99827045</v>
+        <v>-2.043013500000001</v>
       </c>
       <c r="P71">
-        <v>-10.11245955</v>
+        <v>-10.3388865</v>
       </c>
       <c r="Q71">
-        <v>-4.112459550000002</v>
+        <v>-4.338886500000003</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1393162794072368</v>
+        <v>0.1424334887208113</v>
       </c>
       <c r="T71">
-        <v>1.822806347406371</v>
+        <v>1.883566558986583</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.05820189805528699</v>
+        <v>0.05737044236878288</v>
       </c>
       <c r="W71">
-        <v>0.2220759924385634</v>
+        <v>0.222272049689441</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3527387760926484</v>
+        <v>0.3476996507198963</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7661,22 +7661,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1983204813988521</v>
+        <v>0.2002204813988521</v>
       </c>
       <c r="C72">
-        <v>-29.44803555033442</v>
+        <v>-30.80415284880439</v>
       </c>
       <c r="D72">
-        <v>16.75196444966559</v>
+        <v>16.54584715119562</v>
       </c>
       <c r="E72">
-        <v>11.70000000000002</v>
+        <v>12.85000000000001</v>
       </c>
       <c r="F72">
-        <v>80.50000000000001</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="G72">
         <v>34.3</v>
@@ -7697,37 +7697,37 @@
         <v>6.6</v>
       </c>
       <c r="M72">
-        <v>18.9819</v>
+        <v>19.25307</v>
       </c>
       <c r="N72">
-        <v>-12.3819</v>
+        <v>-12.65307</v>
       </c>
       <c r="O72">
-        <v>-2.043013500000001</v>
+        <v>-2.08775655</v>
       </c>
       <c r="P72">
-        <v>-10.3388865</v>
+        <v>-10.56531345</v>
       </c>
       <c r="Q72">
-        <v>-4.338886500000003</v>
+        <v>-4.565313450000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1424334887208113</v>
+        <v>0.1457656779870462</v>
       </c>
       <c r="T72">
-        <v>1.883566558986583</v>
+        <v>1.948517129986121</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.05737044236878288</v>
+        <v>0.05656240796922257</v>
       </c>
       <c r="W72">
-        <v>0.222272049689441</v>
+        <v>0.2224625842008573</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3476996507198963</v>
+        <v>0.3428024725407428</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7743,22 +7743,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2002204813988521</v>
+        <v>0.2021204813988521</v>
       </c>
       <c r="C73">
-        <v>-30.80415284880438</v>
+        <v>-32.15525963472236</v>
       </c>
       <c r="D73">
-        <v>16.54584715119562</v>
+        <v>16.34474036527765</v>
       </c>
       <c r="E73">
-        <v>12.84999999999999</v>
+        <v>14</v>
       </c>
       <c r="F73">
-        <v>81.64999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="G73">
         <v>34.3</v>
@@ -7779,37 +7779,37 @@
         <v>6.6</v>
       </c>
       <c r="M73">
-        <v>19.25307</v>
+        <v>19.52424</v>
       </c>
       <c r="N73">
-        <v>-12.65307</v>
+        <v>-12.92424</v>
       </c>
       <c r="O73">
-        <v>-2.08775655</v>
+        <v>-2.1324996</v>
       </c>
       <c r="P73">
-        <v>-10.56531345</v>
+        <v>-10.7917404</v>
       </c>
       <c r="Q73">
-        <v>-4.565313449999998</v>
+        <v>-4.791740399999998</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1457656779870461</v>
+        <v>0.1493358807722978</v>
       </c>
       <c r="T73">
-        <v>1.94851712998612</v>
+        <v>2.018107027485624</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.05656240796922257</v>
+        <v>0.05577681896965004</v>
       </c>
       <c r="W73">
-        <v>0.2224625842008573</v>
+        <v>0.2226478260869565</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3428024725407429</v>
+        <v>0.3380413270887881</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7825,22 +7825,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2021204813988521</v>
+        <v>0.2040204813988521</v>
       </c>
       <c r="C74">
-        <v>-32.15525963472236</v>
+        <v>-33.50153641519644</v>
       </c>
       <c r="D74">
-        <v>16.34474036527765</v>
+        <v>16.14846358480356</v>
       </c>
       <c r="E74">
-        <v>14</v>
+        <v>15.15000000000001</v>
       </c>
       <c r="F74">
-        <v>82.8</v>
+        <v>83.95</v>
       </c>
       <c r="G74">
         <v>34.3</v>
@@ -7861,37 +7861,37 @@
         <v>6.6</v>
       </c>
       <c r="M74">
-        <v>19.52424</v>
+        <v>19.79541</v>
       </c>
       <c r="N74">
-        <v>-12.92424</v>
+        <v>-13.19541</v>
       </c>
       <c r="O74">
-        <v>-2.1324996</v>
+        <v>-2.17724265</v>
       </c>
       <c r="P74">
-        <v>-10.7917404</v>
+        <v>-11.01816735</v>
       </c>
       <c r="Q74">
-        <v>-4.791740399999998</v>
+        <v>-5.018167350000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1493358807722978</v>
+        <v>0.1531705430231236</v>
       </c>
       <c r="T74">
-        <v>2.018107027485624</v>
+        <v>2.092851732207313</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.05577681896965004</v>
+        <v>0.05501275295636716</v>
       </c>
       <c r="W74">
-        <v>0.2226478260869565</v>
+        <v>0.2228279928528886</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3380413270887881</v>
+        <v>0.3334106239779827</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7907,22 +7907,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2040204813988521</v>
+        <v>0.2059204813988521</v>
       </c>
       <c r="C75">
-        <v>-33.50153641519644</v>
+        <v>-34.84315512969867</v>
       </c>
       <c r="D75">
-        <v>16.14846358480356</v>
+        <v>15.95684487030133</v>
       </c>
       <c r="E75">
-        <v>15.15000000000001</v>
+        <v>16.3</v>
       </c>
       <c r="F75">
-        <v>83.95</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="G75">
         <v>34.3</v>
@@ -7943,37 +7943,37 @@
         <v>6.6</v>
       </c>
       <c r="M75">
-        <v>19.79541</v>
+        <v>20.06658</v>
       </c>
       <c r="N75">
-        <v>-13.19541</v>
+        <v>-13.46658</v>
       </c>
       <c r="O75">
-        <v>-2.17724265</v>
+        <v>-2.2219857</v>
       </c>
       <c r="P75">
-        <v>-11.01816735</v>
+        <v>-11.2445943</v>
       </c>
       <c r="Q75">
-        <v>-5.018167350000001</v>
+        <v>-5.244594299999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1531705430231236</v>
+        <v>0.1573001792932438</v>
       </c>
       <c r="T75">
-        <v>2.092851732207313</v>
+        <v>2.173346029599903</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.05501275295636716</v>
+        <v>0.05426933737587571</v>
       </c>
       <c r="W75">
-        <v>0.2228279928528886</v>
+        <v>0.2230032902467685</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3334106239779827</v>
+        <v>0.3289050750053073</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7989,22 +7989,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2059204813988521</v>
+        <v>0.2078204813988521</v>
       </c>
       <c r="C76">
-        <v>-34.84315512969867</v>
+        <v>-36.18027965242453</v>
       </c>
       <c r="D76">
-        <v>15.95684487030133</v>
+        <v>15.76972034757548</v>
       </c>
       <c r="E76">
-        <v>16.3</v>
+        <v>17.45</v>
       </c>
       <c r="F76">
-        <v>85.09999999999999</v>
+        <v>86.25</v>
       </c>
       <c r="G76">
         <v>34.3</v>
@@ -8025,37 +8025,37 @@
         <v>6.6</v>
       </c>
       <c r="M76">
-        <v>20.06658</v>
+        <v>20.33775</v>
       </c>
       <c r="N76">
-        <v>-13.46658</v>
+        <v>-13.73775</v>
       </c>
       <c r="O76">
-        <v>-2.2219857</v>
+        <v>-2.26672875</v>
       </c>
       <c r="P76">
-        <v>-11.2445943</v>
+        <v>-11.47102125</v>
       </c>
       <c r="Q76">
-        <v>-5.244594299999999</v>
+        <v>-5.47102125</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1573001792932438</v>
+        <v>0.1617601864649735</v>
       </c>
       <c r="T76">
-        <v>2.173346029599903</v>
+        <v>2.260279870783899</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.05426933737587571</v>
+        <v>0.05354574621086404</v>
       </c>
       <c r="W76">
-        <v>0.2230032902467685</v>
+        <v>0.2231739130434783</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3289050750053073</v>
+        <v>0.3245196740052365</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -8071,22 +8071,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2078204813988521</v>
+        <v>0.2097204813988521</v>
       </c>
       <c r="C77">
-        <v>-36.18027965242453</v>
+        <v>-37.51306625971547</v>
       </c>
       <c r="D77">
-        <v>15.76972034757548</v>
+        <v>15.58693374028454</v>
       </c>
       <c r="E77">
-        <v>17.45</v>
+        <v>18.60000000000001</v>
       </c>
       <c r="F77">
-        <v>86.25</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="G77">
         <v>34.3</v>
@@ -8107,37 +8107,37 @@
         <v>6.6</v>
       </c>
       <c r="M77">
-        <v>20.33775</v>
+        <v>20.60892</v>
       </c>
       <c r="N77">
-        <v>-13.73775</v>
+        <v>-14.00892</v>
       </c>
       <c r="O77">
-        <v>-2.26672875</v>
+        <v>-2.311471800000001</v>
       </c>
       <c r="P77">
-        <v>-11.47102125</v>
+        <v>-11.6974482</v>
       </c>
       <c r="Q77">
-        <v>-5.47102125</v>
+        <v>-5.6974482</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1617601864649735</v>
+        <v>0.1665918609010141</v>
       </c>
       <c r="T77">
-        <v>2.260279870783899</v>
+        <v>2.354458198733229</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.05354574621086404</v>
+        <v>0.05284119691861582</v>
       </c>
       <c r="W77">
-        <v>0.2231739130434783</v>
+        <v>0.2233400457665904</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3245196740052365</v>
+        <v>0.3202496782946413</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -8153,22 +8153,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2097204813988521</v>
+        <v>0.2116204813988521</v>
       </c>
       <c r="C78">
-        <v>-37.51306625971547</v>
+        <v>-38.84166406534664</v>
       </c>
       <c r="D78">
-        <v>15.58693374028454</v>
+        <v>15.40833593465336</v>
       </c>
       <c r="E78">
-        <v>18.60000000000001</v>
+        <v>19.75</v>
       </c>
       <c r="F78">
-        <v>87.40000000000001</v>
+        <v>88.55</v>
       </c>
       <c r="G78">
         <v>34.3</v>
@@ -8189,37 +8189,37 @@
         <v>6.6</v>
       </c>
       <c r="M78">
-        <v>20.60892</v>
+        <v>20.88009</v>
       </c>
       <c r="N78">
-        <v>-14.00892</v>
+        <v>-14.28009</v>
       </c>
       <c r="O78">
-        <v>-2.311471800000001</v>
+        <v>-2.35621485</v>
       </c>
       <c r="P78">
-        <v>-11.6974482</v>
+        <v>-11.92387515</v>
       </c>
       <c r="Q78">
-        <v>-5.6974482</v>
+        <v>-5.923875149999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1665918609010141</v>
+        <v>0.1718436809401886</v>
       </c>
       <c r="T78">
-        <v>2.354458198733229</v>
+        <v>2.456825946504238</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.05284119691861582</v>
+        <v>0.05215494760798445</v>
       </c>
       <c r="W78">
-        <v>0.2233400457665904</v>
+        <v>0.2235018633540373</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3202496782946413</v>
+        <v>0.3160905915635421</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -8235,22 +8235,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2116204813988521</v>
+        <v>0.2135204813988521</v>
       </c>
       <c r="C79">
-        <v>-38.84166406534664</v>
+        <v>-40.16621542622798</v>
       </c>
       <c r="D79">
-        <v>15.40833593465336</v>
+        <v>15.23378457377203</v>
       </c>
       <c r="E79">
-        <v>19.75</v>
+        <v>20.90000000000001</v>
       </c>
       <c r="F79">
-        <v>88.55</v>
+        <v>89.7</v>
       </c>
       <c r="G79">
         <v>34.3</v>
@@ -8271,37 +8271,37 @@
         <v>6.6</v>
       </c>
       <c r="M79">
-        <v>20.88009</v>
+        <v>21.15126</v>
       </c>
       <c r="N79">
-        <v>-14.28009</v>
+        <v>-14.55126</v>
       </c>
       <c r="O79">
-        <v>-2.35621485</v>
+        <v>-2.4009579</v>
       </c>
       <c r="P79">
-        <v>-11.92387515</v>
+        <v>-12.1503021</v>
       </c>
       <c r="Q79">
-        <v>-5.923875149999999</v>
+        <v>-6.150302100000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1718436809401886</v>
+        <v>0.1775729391647427</v>
       </c>
       <c r="T79">
-        <v>2.456825946504238</v>
+        <v>2.568499853163522</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.05215494760798445</v>
+        <v>0.05148629443352311</v>
       </c>
       <c r="W79">
-        <v>0.2235018633540373</v>
+        <v>0.2236595317725752</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3160905915635421</v>
+        <v>0.3120381480819582</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8317,22 +8317,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2135204813988521</v>
+        <v>0.2154204813988521</v>
       </c>
       <c r="C80">
-        <v>-40.16621542622798</v>
+        <v>-41.48685632083849</v>
       </c>
       <c r="D80">
-        <v>15.23378457377203</v>
+        <v>15.06314367916152</v>
       </c>
       <c r="E80">
-        <v>20.90000000000001</v>
+        <v>22.05000000000001</v>
       </c>
       <c r="F80">
-        <v>89.7</v>
+        <v>90.85000000000001</v>
       </c>
       <c r="G80">
         <v>34.3</v>
@@ -8353,37 +8353,37 @@
         <v>6.6</v>
       </c>
       <c r="M80">
-        <v>21.15126</v>
+        <v>21.42243</v>
       </c>
       <c r="N80">
-        <v>-14.55126</v>
+        <v>-14.82243</v>
       </c>
       <c r="O80">
-        <v>-2.4009579</v>
+        <v>-2.44570095</v>
       </c>
       <c r="P80">
-        <v>-12.1503021</v>
+        <v>-12.37672905</v>
       </c>
       <c r="Q80">
-        <v>-6.150302100000001</v>
+        <v>-6.376729050000002</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1775729391647427</v>
+        <v>0.1838478410297304</v>
       </c>
       <c r="T80">
-        <v>2.568499853163522</v>
+        <v>2.690809369980832</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.05148629443352311</v>
+        <v>0.05083456918752914</v>
       </c>
       <c r="W80">
-        <v>0.2236595317725752</v>
+        <v>0.2238132085855806</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3120381480819582</v>
+        <v>0.3080882981062372</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8399,22 +8399,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2154204813988521</v>
+        <v>0.2173204813988521</v>
       </c>
       <c r="C81">
-        <v>-41.48685632083849</v>
+        <v>-42.80371670250832</v>
       </c>
       <c r="D81">
-        <v>15.06314367916152</v>
+        <v>14.89628329749168</v>
       </c>
       <c r="E81">
-        <v>22.05000000000001</v>
+        <v>23.2</v>
       </c>
       <c r="F81">
-        <v>90.85000000000001</v>
+        <v>92</v>
       </c>
       <c r="G81">
         <v>34.3</v>
@@ -8435,37 +8435,37 @@
         <v>6.6</v>
       </c>
       <c r="M81">
-        <v>21.42243</v>
+        <v>21.6936</v>
       </c>
       <c r="N81">
-        <v>-14.82243</v>
+        <v>-15.0936</v>
       </c>
       <c r="O81">
-        <v>-2.44570095</v>
+        <v>-2.490444</v>
       </c>
       <c r="P81">
-        <v>-12.37672905</v>
+        <v>-12.603156</v>
       </c>
       <c r="Q81">
-        <v>-6.376729050000002</v>
+        <v>-6.603156</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1838478410297304</v>
+        <v>0.190750233081217</v>
       </c>
       <c r="T81">
-        <v>2.690809369980832</v>
+        <v>2.825349838479874</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.05083456918752914</v>
+        <v>0.05019913707268503</v>
       </c>
       <c r="W81">
-        <v>0.2238132085855806</v>
+        <v>0.2239630434782609</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3080882981062372</v>
+        <v>0.3042371943799093</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8481,22 +8481,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2173204813988521</v>
+        <v>0.2192204813988521</v>
       </c>
       <c r="C82">
-        <v>-42.80371670250832</v>
+        <v>-44.11692082947728</v>
       </c>
       <c r="D82">
-        <v>14.89628329749168</v>
+        <v>14.73307917052273</v>
       </c>
       <c r="E82">
-        <v>23.2</v>
+        <v>24.35000000000001</v>
       </c>
       <c r="F82">
-        <v>92</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="G82">
         <v>34.3</v>
@@ -8517,37 +8517,37 @@
         <v>6.6</v>
       </c>
       <c r="M82">
-        <v>21.6936</v>
+        <v>21.96477</v>
       </c>
       <c r="N82">
-        <v>-15.0936</v>
+        <v>-15.36477</v>
       </c>
       <c r="O82">
-        <v>-2.490444</v>
+        <v>-2.53518705</v>
       </c>
       <c r="P82">
-        <v>-12.603156</v>
+        <v>-12.82958295</v>
       </c>
       <c r="Q82">
-        <v>-6.603156</v>
+        <v>-6.829582950000002</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.190750233081217</v>
+        <v>0.1983791927170705</v>
       </c>
       <c r="T82">
-        <v>2.825349838479874</v>
+        <v>2.974052461557762</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.05019913707268503</v>
+        <v>0.04957939463968892</v>
       </c>
       <c r="W82">
-        <v>0.2239630434782609</v>
+        <v>0.2241091787439614</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3042371943799093</v>
+        <v>0.3004811796344783</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8563,22 +8563,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2192204813988521</v>
+        <v>0.2211204813988521</v>
       </c>
       <c r="C83">
-        <v>-44.11692082947728</v>
+        <v>-45.4265875734917</v>
       </c>
       <c r="D83">
-        <v>14.73307917052273</v>
+        <v>14.57341242650831</v>
       </c>
       <c r="E83">
-        <v>24.35000000000001</v>
+        <v>25.50000000000001</v>
       </c>
       <c r="F83">
-        <v>93.15000000000001</v>
+        <v>94.30000000000001</v>
       </c>
       <c r="G83">
         <v>34.3</v>
@@ -8599,37 +8599,37 @@
         <v>6.6</v>
       </c>
       <c r="M83">
-        <v>21.96477</v>
+        <v>22.23594</v>
       </c>
       <c r="N83">
-        <v>-15.36477</v>
+        <v>-15.63594</v>
       </c>
       <c r="O83">
-        <v>-2.53518705</v>
+        <v>-2.579930100000001</v>
       </c>
       <c r="P83">
-        <v>-12.82958295</v>
+        <v>-13.0560099</v>
       </c>
       <c r="Q83">
-        <v>-6.829582950000002</v>
+        <v>-7.056009900000003</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1983791927170705</v>
+        <v>0.2068558145346855</v>
       </c>
       <c r="T83">
-        <v>2.974052461557762</v>
+        <v>3.139277598310972</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.04957939463968892</v>
+        <v>0.04897476787579027</v>
       </c>
       <c r="W83">
-        <v>0.2241091787439614</v>
+        <v>0.2242517497348887</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3004811796344783</v>
+        <v>0.2968167750047895</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8645,22 +8645,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2211204813988521</v>
+        <v>0.2230204813988521</v>
       </c>
       <c r="C84">
-        <v>-45.4265875734917</v>
+        <v>-46.73283070855037</v>
       </c>
       <c r="D84">
-        <v>14.57341242650831</v>
+        <v>14.41716929144964</v>
       </c>
       <c r="E84">
-        <v>25.50000000000001</v>
+        <v>26.65000000000001</v>
       </c>
       <c r="F84">
-        <v>94.30000000000001</v>
+        <v>95.45</v>
       </c>
       <c r="G84">
         <v>34.3</v>
@@ -8681,37 +8681,37 @@
         <v>6.6</v>
       </c>
       <c r="M84">
-        <v>22.23594</v>
+        <v>22.50711</v>
       </c>
       <c r="N84">
-        <v>-15.63594</v>
+        <v>-15.90711</v>
       </c>
       <c r="O84">
-        <v>-2.579930100000001</v>
+        <v>-2.62467315</v>
       </c>
       <c r="P84">
-        <v>-13.0560099</v>
+        <v>-13.28243685</v>
       </c>
       <c r="Q84">
-        <v>-7.056009900000003</v>
+        <v>-7.28243685</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2068558145346855</v>
+        <v>0.2163296859779023</v>
       </c>
       <c r="T84">
-        <v>3.139277598310972</v>
+        <v>3.323940986446912</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.04897476787579027</v>
+        <v>0.04838471043150364</v>
       </c>
       <c r="W84">
-        <v>0.2242517497348887</v>
+        <v>0.2243908852802514</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2968167750047895</v>
+        <v>0.2932406692818402</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8727,22 +8727,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2230204813988521</v>
+        <v>0.2249204813988521</v>
       </c>
       <c r="C85">
-        <v>-46.73283070855037</v>
+        <v>-48.03575918127348</v>
       </c>
       <c r="D85">
-        <v>14.41716929144964</v>
+        <v>14.26424081872653</v>
       </c>
       <c r="E85">
-        <v>26.65000000000001</v>
+        <v>27.80000000000001</v>
       </c>
       <c r="F85">
-        <v>95.45</v>
+        <v>96.60000000000001</v>
       </c>
       <c r="G85">
         <v>34.3</v>
@@ -8763,37 +8763,37 @@
         <v>6.6</v>
       </c>
       <c r="M85">
-        <v>22.50711</v>
+        <v>22.77828</v>
       </c>
       <c r="N85">
-        <v>-15.90711</v>
+        <v>-16.17828</v>
       </c>
       <c r="O85">
-        <v>-2.62467315</v>
+        <v>-2.6694162</v>
       </c>
       <c r="P85">
-        <v>-13.28243685</v>
+        <v>-13.5088638</v>
       </c>
       <c r="Q85">
-        <v>-7.28243685</v>
+        <v>-7.5088638</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2163296859779023</v>
+        <v>0.2269877913515213</v>
       </c>
       <c r="T85">
-        <v>3.323940986446912</v>
+        <v>3.531687298099845</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.04838471043150364</v>
+        <v>0.04780870197398573</v>
       </c>
       <c r="W85">
-        <v>0.2243908852802514</v>
+        <v>0.2245267080745342</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2932406692818402</v>
+        <v>0.2897497089332469</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8809,22 +8809,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2249204813988521</v>
+        <v>0.2268204813988521</v>
       </c>
       <c r="C86">
-        <v>-48.03575918127346</v>
+        <v>-49.33547736424452</v>
       </c>
       <c r="D86">
-        <v>14.26424081872653</v>
+        <v>14.11452263575548</v>
       </c>
       <c r="E86">
-        <v>27.8</v>
+        <v>28.95</v>
       </c>
       <c r="F86">
-        <v>96.59999999999999</v>
+        <v>97.75</v>
       </c>
       <c r="G86">
         <v>34.3</v>
@@ -8845,37 +8845,37 @@
         <v>6.6</v>
       </c>
       <c r="M86">
-        <v>22.77828</v>
+        <v>23.04945</v>
       </c>
       <c r="N86">
-        <v>-16.17828</v>
+        <v>-16.44945</v>
       </c>
       <c r="O86">
-        <v>-2.6694162</v>
+        <v>-2.71415925</v>
       </c>
       <c r="P86">
-        <v>-13.5088638</v>
+        <v>-13.73529075</v>
       </c>
       <c r="Q86">
-        <v>-7.5088638</v>
+        <v>-7.735290749999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2269877913515212</v>
+        <v>0.2390669774416226</v>
       </c>
       <c r="T86">
-        <v>3.531687298099842</v>
+        <v>3.767133117973165</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.04780870197398574</v>
+        <v>0.04724624665664474</v>
       </c>
       <c r="W86">
-        <v>0.2245267080745341</v>
+        <v>0.2246593350383632</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2897497089332468</v>
+        <v>0.28634088882815</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8891,22 +8891,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2268204813988521</v>
+        <v>0.2287204813988521</v>
       </c>
       <c r="C87">
-        <v>-49.33547736424452</v>
+        <v>-50.63208529356359</v>
       </c>
       <c r="D87">
-        <v>14.11452263575548</v>
+        <v>13.9679147064364</v>
       </c>
       <c r="E87">
-        <v>28.95</v>
+        <v>30.09999999999999</v>
       </c>
       <c r="F87">
-        <v>97.75</v>
+        <v>98.89999999999999</v>
       </c>
       <c r="G87">
         <v>34.3</v>
@@ -8927,37 +8927,37 @@
         <v>6.6</v>
       </c>
       <c r="M87">
-        <v>23.04945</v>
+        <v>23.32062</v>
       </c>
       <c r="N87">
-        <v>-16.44945</v>
+        <v>-16.72062</v>
       </c>
       <c r="O87">
-        <v>-2.71415925</v>
+        <v>-2.758902299999999</v>
       </c>
       <c r="P87">
-        <v>-13.73529075</v>
+        <v>-13.9617177</v>
       </c>
       <c r="Q87">
-        <v>-7.735290749999999</v>
+        <v>-7.961717699999998</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2390669774416226</v>
+        <v>0.2528717615445956</v>
       </c>
       <c r="T87">
-        <v>3.767133117973165</v>
+        <v>4.036214054971248</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04724624665664474</v>
+        <v>0.04669687169552096</v>
       </c>
       <c r="W87">
-        <v>0.2246593350383632</v>
+        <v>0.2247888776541962</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.28634088882815</v>
+        <v>0.283011343609218</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8973,22 +8973,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2287204813988521</v>
+        <v>0.2306204813988521</v>
       </c>
       <c r="C88">
-        <v>-50.63208529356359</v>
+        <v>-51.92567889174797</v>
       </c>
       <c r="D88">
-        <v>13.9679147064364</v>
+        <v>13.82432110825203</v>
       </c>
       <c r="E88">
-        <v>30.09999999999999</v>
+        <v>31.25</v>
       </c>
       <c r="F88">
-        <v>98.89999999999999</v>
+        <v>100.05</v>
       </c>
       <c r="G88">
         <v>34.3</v>
@@ -9009,37 +9009,37 @@
         <v>6.6</v>
       </c>
       <c r="M88">
-        <v>23.32062</v>
+        <v>23.59179</v>
       </c>
       <c r="N88">
-        <v>-16.72062</v>
+        <v>-16.99179</v>
       </c>
       <c r="O88">
-        <v>-2.758902299999999</v>
+        <v>-2.80364535</v>
       </c>
       <c r="P88">
-        <v>-13.9617177</v>
+        <v>-14.18814465</v>
       </c>
       <c r="Q88">
-        <v>-7.961717699999998</v>
+        <v>-8.188144650000002</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2528717615445956</v>
+        <v>0.2688003585864875</v>
       </c>
       <c r="T88">
-        <v>4.036214054971248</v>
+        <v>4.346692059199805</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.04669687169552096</v>
+        <v>0.0461601260438483</v>
       </c>
       <c r="W88">
-        <v>0.2247888776541962</v>
+        <v>0.2249154422788606</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.283011343609218</v>
+        <v>0.2797583396596867</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -9055,22 +9055,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2306204813988521</v>
+        <v>0.2325204813988521</v>
       </c>
       <c r="C89">
-        <v>-51.92567889174797</v>
+        <v>-53.21635017702371</v>
       </c>
       <c r="D89">
-        <v>13.82432110825203</v>
+        <v>13.6836498229763</v>
       </c>
       <c r="E89">
-        <v>31.25</v>
+        <v>32.40000000000001</v>
       </c>
       <c r="F89">
-        <v>100.05</v>
+        <v>101.2</v>
       </c>
       <c r="G89">
         <v>34.3</v>
@@ -9091,37 +9091,37 @@
         <v>6.6</v>
       </c>
       <c r="M89">
-        <v>23.59179</v>
+        <v>23.86296</v>
       </c>
       <c r="N89">
-        <v>-16.99179</v>
+        <v>-17.26296</v>
       </c>
       <c r="O89">
-        <v>-2.80364535</v>
+        <v>-2.8483884</v>
       </c>
       <c r="P89">
-        <v>-14.18814465</v>
+        <v>-14.4145716</v>
       </c>
       <c r="Q89">
-        <v>-8.188144650000002</v>
+        <v>-8.414571599999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2688003585864875</v>
+        <v>0.2873837218020283</v>
       </c>
       <c r="T89">
-        <v>4.346692059199805</v>
+        <v>4.708916397466457</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.0461601260438483</v>
+        <v>0.04563557915698639</v>
       </c>
       <c r="W89">
-        <v>0.2249154422788606</v>
+        <v>0.2250391304347826</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2797583396596867</v>
+        <v>0.2765792676180994</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -9137,22 +9137,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2325204813988521</v>
+        <v>0.2344204813988521</v>
       </c>
       <c r="C90">
-        <v>-53.21635017702371</v>
+        <v>-54.50418745996797</v>
       </c>
       <c r="D90">
-        <v>13.6836498229763</v>
+        <v>13.54581254003205</v>
       </c>
       <c r="E90">
-        <v>32.40000000000001</v>
+        <v>33.55000000000001</v>
       </c>
       <c r="F90">
-        <v>101.2</v>
+        <v>102.35</v>
       </c>
       <c r="G90">
         <v>34.3</v>
@@ -9173,37 +9173,37 @@
         <v>6.6</v>
       </c>
       <c r="M90">
-        <v>23.86296</v>
+        <v>24.13413</v>
       </c>
       <c r="N90">
-        <v>-17.26296</v>
+        <v>-17.53413</v>
       </c>
       <c r="O90">
-        <v>-2.8483884</v>
+        <v>-2.893131450000001</v>
       </c>
       <c r="P90">
-        <v>-14.4145716</v>
+        <v>-14.64099855</v>
       </c>
       <c r="Q90">
-        <v>-8.414571599999999</v>
+        <v>-8.640998550000004</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2873837218020283</v>
+        <v>0.3093458783294853</v>
       </c>
       <c r="T90">
-        <v>4.708916397466457</v>
+        <v>5.136999706327043</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.04563557915698639</v>
+        <v>0.04512281984061575</v>
       </c>
       <c r="W90">
-        <v>0.2250391304347826</v>
+        <v>0.2251600390815828</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -9211,7 +9211,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2765792676180994</v>
+        <v>0.2734716353976712</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -9219,22 +9219,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2344204813988521</v>
+        <v>0.2363204813988521</v>
       </c>
       <c r="C91">
-        <v>-54.50418745996797</v>
+        <v>-55.78927552838502</v>
       </c>
       <c r="D91">
-        <v>13.54581254003205</v>
+        <v>13.41072447161498</v>
       </c>
       <c r="E91">
-        <v>33.55000000000001</v>
+        <v>34.7</v>
       </c>
       <c r="F91">
-        <v>102.35</v>
+        <v>103.5</v>
       </c>
       <c r="G91">
         <v>34.3</v>
@@ -9255,37 +9255,37 @@
         <v>6.6</v>
       </c>
       <c r="M91">
-        <v>24.13413</v>
+        <v>24.4053</v>
       </c>
       <c r="N91">
-        <v>-17.53413</v>
+        <v>-17.8053</v>
       </c>
       <c r="O91">
-        <v>-2.893131450000001</v>
+        <v>-2.9378745</v>
       </c>
       <c r="P91">
-        <v>-14.64099855</v>
+        <v>-14.8674255</v>
       </c>
       <c r="Q91">
-        <v>-8.640998550000004</v>
+        <v>-8.867425500000003</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3093458783294853</v>
+        <v>0.3357004661624339</v>
       </c>
       <c r="T91">
-        <v>5.136999706327043</v>
+        <v>5.650699676959748</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.04512281984061575</v>
+        <v>0.04462145517572003</v>
       </c>
       <c r="W91">
-        <v>0.2251600390815828</v>
+        <v>0.2252782608695652</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2734716353976712</v>
+        <v>0.2704330616710304</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9301,22 +9301,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2363204813988521</v>
+        <v>0.2382204813988521</v>
       </c>
       <c r="C92">
-        <v>-55.78927552838502</v>
+        <v>-57.07169582122928</v>
       </c>
       <c r="D92">
-        <v>13.41072447161498</v>
+        <v>13.27830417877072</v>
       </c>
       <c r="E92">
-        <v>34.7</v>
+        <v>35.85000000000001</v>
       </c>
       <c r="F92">
-        <v>103.5</v>
+        <v>104.65</v>
       </c>
       <c r="G92">
         <v>34.3</v>
@@ -9337,37 +9337,37 @@
         <v>6.6</v>
       </c>
       <c r="M92">
-        <v>24.4053</v>
+        <v>24.67647</v>
       </c>
       <c r="N92">
-        <v>-17.8053</v>
+        <v>-18.07647</v>
       </c>
       <c r="O92">
-        <v>-2.9378745</v>
+        <v>-2.98261755</v>
       </c>
       <c r="P92">
-        <v>-14.8674255</v>
+        <v>-15.09385245</v>
       </c>
       <c r="Q92">
-        <v>-8.867425500000003</v>
+        <v>-9.09385245</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3357004661624339</v>
+        <v>0.3679116290693711</v>
       </c>
       <c r="T92">
-        <v>5.650699676959748</v>
+        <v>6.278555196621944</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.04462145517572003</v>
+        <v>0.04413110951444837</v>
       </c>
       <c r="W92">
-        <v>0.2252782608695652</v>
+        <v>0.2253938843764931</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9375,7 +9375,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2704330616710304</v>
+        <v>0.2674612697845357</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9383,22 +9383,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2382204813988521</v>
+        <v>0.2401204813988521</v>
       </c>
       <c r="C93">
-        <v>-57.07169582122928</v>
+        <v>-58.3515265923248</v>
       </c>
       <c r="D93">
-        <v>13.27830417877072</v>
+        <v>13.14847340767521</v>
       </c>
       <c r="E93">
-        <v>35.85000000000001</v>
+        <v>37.00000000000001</v>
       </c>
       <c r="F93">
-        <v>104.65</v>
+        <v>105.8</v>
       </c>
       <c r="G93">
         <v>34.3</v>
@@ -9419,37 +9419,37 @@
         <v>6.6</v>
       </c>
       <c r="M93">
-        <v>24.67647</v>
+        <v>24.94764</v>
       </c>
       <c r="N93">
-        <v>-18.07647</v>
+        <v>-18.34764000000001</v>
       </c>
       <c r="O93">
-        <v>-2.98261755</v>
+        <v>-3.027360600000001</v>
       </c>
       <c r="P93">
-        <v>-15.09385245</v>
+        <v>-15.3202794</v>
       </c>
       <c r="Q93">
-        <v>-9.09385245</v>
+        <v>-9.320279400000004</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3679116290693711</v>
+        <v>0.4081755827030426</v>
       </c>
       <c r="T93">
-        <v>6.278555196621944</v>
+        <v>7.063374596199689</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.04413110951444837</v>
+        <v>0.04365142354146524</v>
       </c>
       <c r="W93">
-        <v>0.2253938843764931</v>
+        <v>0.2255069943289225</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2674612697845357</v>
+        <v>0.2645540820694862</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9465,22 +9465,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2401204813988521</v>
+        <v>0.2420204813988521</v>
       </c>
       <c r="C94">
-        <v>-58.3515265923248</v>
+        <v>-59.62884306457318</v>
       </c>
       <c r="D94">
-        <v>13.14847340767521</v>
+        <v>13.02115693542683</v>
       </c>
       <c r="E94">
-        <v>37.00000000000001</v>
+        <v>38.15000000000001</v>
       </c>
       <c r="F94">
-        <v>105.8</v>
+        <v>106.95</v>
       </c>
       <c r="G94">
         <v>34.3</v>
@@ -9501,37 +9501,37 @@
         <v>6.6</v>
       </c>
       <c r="M94">
-        <v>24.94764</v>
+        <v>25.21881</v>
       </c>
       <c r="N94">
-        <v>-18.34764000000001</v>
+        <v>-18.61881</v>
       </c>
       <c r="O94">
-        <v>-3.027360600000001</v>
+        <v>-3.072103650000001</v>
       </c>
       <c r="P94">
-        <v>-15.3202794</v>
+        <v>-15.54670635</v>
       </c>
       <c r="Q94">
-        <v>-9.320279400000004</v>
+        <v>-9.546706350000003</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4081755827030426</v>
+        <v>0.4599435230891915</v>
       </c>
       <c r="T94">
-        <v>7.063374596199689</v>
+        <v>8.072428109942502</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.04365142354146524</v>
+        <v>0.04318205339585809</v>
       </c>
       <c r="W94">
-        <v>0.2255069943289225</v>
+        <v>0.2256176718092567</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2645540820694862</v>
+        <v>0.261709414520352</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9547,22 +9547,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2420204813988521</v>
+        <v>0.2439204813988521</v>
       </c>
       <c r="C95">
-        <v>-59.62884306457318</v>
+        <v>-60.90371757528824</v>
       </c>
       <c r="D95">
-        <v>13.02115693542683</v>
+        <v>12.89628242471177</v>
       </c>
       <c r="E95">
-        <v>38.15000000000001</v>
+        <v>39.30000000000001</v>
       </c>
       <c r="F95">
-        <v>106.95</v>
+        <v>108.1</v>
       </c>
       <c r="G95">
         <v>34.3</v>
@@ -9583,37 +9583,37 @@
         <v>6.6</v>
       </c>
       <c r="M95">
-        <v>25.21881</v>
+        <v>25.48998</v>
       </c>
       <c r="N95">
-        <v>-18.61881</v>
+        <v>-18.88998</v>
       </c>
       <c r="O95">
-        <v>-3.072103650000001</v>
+        <v>-3.1168467</v>
       </c>
       <c r="P95">
-        <v>-15.54670635</v>
+        <v>-15.7731333</v>
       </c>
       <c r="Q95">
-        <v>-9.546706350000003</v>
+        <v>-9.773133300000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4599435230891915</v>
+        <v>0.5289674436040569</v>
       </c>
       <c r="T95">
-        <v>8.072428109942502</v>
+        <v>9.417832794932922</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.04318205339585809</v>
+        <v>0.04272266984909364</v>
       </c>
       <c r="W95">
-        <v>0.2256176718092567</v>
+        <v>0.2257259944495837</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.261709414520352</v>
+        <v>0.2589252718126888</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9629,22 +9629,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2439204813988521</v>
+        <v>0.2458204813988521</v>
       </c>
       <c r="C96">
-        <v>-60.90371757528824</v>
+        <v>-62.17621971324727</v>
       </c>
       <c r="D96">
-        <v>12.89628242471177</v>
+        <v>12.77378028675275</v>
       </c>
       <c r="E96">
-        <v>39.30000000000001</v>
+        <v>40.45000000000002</v>
       </c>
       <c r="F96">
-        <v>108.1</v>
+        <v>109.25</v>
       </c>
       <c r="G96">
         <v>34.3</v>
@@ -9665,37 +9665,37 @@
         <v>6.6</v>
       </c>
       <c r="M96">
-        <v>25.48998</v>
+        <v>25.76115</v>
       </c>
       <c r="N96">
-        <v>-18.88998</v>
+        <v>-19.16115000000001</v>
       </c>
       <c r="O96">
-        <v>-3.1168467</v>
+        <v>-3.161589750000001</v>
       </c>
       <c r="P96">
-        <v>-15.7731333</v>
+        <v>-15.99956025000001</v>
       </c>
       <c r="Q96">
-        <v>-9.773133300000001</v>
+        <v>-9.999560250000005</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5289674436040569</v>
+        <v>0.6256009323248686</v>
       </c>
       <c r="T96">
-        <v>9.417832794932922</v>
+        <v>11.30139935391951</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04272266984909364</v>
+        <v>0.04227295753489266</v>
       </c>
       <c r="W96">
-        <v>0.2257259944495837</v>
+        <v>0.2258320366132723</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2589252718126888</v>
+        <v>0.256199742635713</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9711,22 +9711,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2458204813988521</v>
+        <v>0.2477204813988521</v>
       </c>
       <c r="C97">
-        <v>-62.17621971324727</v>
+        <v>-63.44641644800488</v>
       </c>
       <c r="D97">
-        <v>12.77378028675275</v>
+        <v>12.65358355199512</v>
       </c>
       <c r="E97">
-        <v>40.45000000000002</v>
+        <v>41.60000000000001</v>
       </c>
       <c r="F97">
-        <v>109.25</v>
+        <v>110.4</v>
       </c>
       <c r="G97">
         <v>34.3</v>
@@ -9747,37 +9747,37 @@
         <v>6.6</v>
       </c>
       <c r="M97">
-        <v>25.76115</v>
+        <v>26.03232</v>
       </c>
       <c r="N97">
-        <v>-19.16115000000001</v>
+        <v>-19.43232</v>
       </c>
       <c r="O97">
-        <v>-3.161589750000001</v>
+        <v>-3.206332800000001</v>
       </c>
       <c r="P97">
-        <v>-15.99956025000001</v>
+        <v>-16.2259872</v>
       </c>
       <c r="Q97">
-        <v>-9.999560250000005</v>
+        <v>-10.2259872</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6256009323248686</v>
+        <v>0.770551165406086</v>
       </c>
       <c r="T97">
-        <v>11.30139935391951</v>
+        <v>14.1267491923994</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.04227295753489266</v>
+        <v>0.04183261422723752</v>
       </c>
       <c r="W97">
-        <v>0.2258320366132723</v>
+        <v>0.2259358695652174</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.256199742635713</v>
+        <v>0.253530995316591</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9793,22 +9793,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2477204813988521</v>
+        <v>0.2496204813988521</v>
       </c>
       <c r="C98">
-        <v>-63.44641644800487</v>
+        <v>-64.71437225197408</v>
       </c>
       <c r="D98">
-        <v>12.65358355199512</v>
+        <v>12.53562774802593</v>
       </c>
       <c r="E98">
-        <v>41.59999999999999</v>
+        <v>42.75</v>
       </c>
       <c r="F98">
-        <v>110.4</v>
+        <v>111.55</v>
       </c>
       <c r="G98">
         <v>34.3</v>
@@ -9829,37 +9829,37 @@
         <v>6.6</v>
       </c>
       <c r="M98">
-        <v>26.03232</v>
+        <v>26.30349</v>
       </c>
       <c r="N98">
-        <v>-19.43232</v>
+        <v>-19.70349</v>
       </c>
       <c r="O98">
-        <v>-3.2063328</v>
+        <v>-3.25107585</v>
       </c>
       <c r="P98">
-        <v>-16.2259872</v>
+        <v>-16.45241415</v>
       </c>
       <c r="Q98">
-        <v>-10.2259872</v>
+        <v>-10.45241415</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7705511654060841</v>
+        <v>1.012134887208112</v>
       </c>
       <c r="T98">
-        <v>14.12674919239936</v>
+        <v>18.83566558986581</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04183261422723753</v>
+        <v>0.0414013501630392</v>
       </c>
       <c r="W98">
-        <v>0.2259358695652174</v>
+        <v>0.2260375616315554</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2535309953165912</v>
+        <v>0.250917273715389</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9875,22 +9875,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2496204813988521</v>
+        <v>0.2515204813988521</v>
       </c>
       <c r="C99">
-        <v>-64.71437225197408</v>
+        <v>-65.98014921574207</v>
       </c>
       <c r="D99">
-        <v>12.53562774802593</v>
+        <v>12.41985078425793</v>
       </c>
       <c r="E99">
-        <v>42.75</v>
+        <v>43.90000000000001</v>
       </c>
       <c r="F99">
-        <v>111.55</v>
+        <v>112.7</v>
       </c>
       <c r="G99">
         <v>34.3</v>
@@ -9911,37 +9911,37 @@
         <v>6.6</v>
       </c>
       <c r="M99">
-        <v>26.30349</v>
+        <v>26.57466</v>
       </c>
       <c r="N99">
-        <v>-19.70349</v>
+        <v>-19.97466</v>
       </c>
       <c r="O99">
-        <v>-3.25107585</v>
+        <v>-3.2958189</v>
       </c>
       <c r="P99">
-        <v>-16.45241415</v>
+        <v>-16.6788411</v>
       </c>
       <c r="Q99">
-        <v>-10.45241415</v>
+        <v>-10.6788411</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.012134887208112</v>
+        <v>1.495302330812168</v>
       </c>
       <c r="T99">
-        <v>18.83566558986581</v>
+        <v>28.25349838479871</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.0414013501630392</v>
+        <v>0.04097888740627349</v>
       </c>
       <c r="W99">
-        <v>0.2260375616315554</v>
+        <v>0.2261371783496007</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.250917273715389</v>
+        <v>0.2483568933713546</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9957,22 +9957,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2515204813988521</v>
+        <v>0.2534204813988521</v>
       </c>
       <c r="C100">
-        <v>-65.98014921574207</v>
+        <v>-67.2438071570545</v>
       </c>
       <c r="D100">
-        <v>12.41985078425793</v>
+        <v>12.3061928429455</v>
       </c>
       <c r="E100">
-        <v>43.90000000000001</v>
+        <v>45.05</v>
       </c>
       <c r="F100">
-        <v>112.7</v>
+        <v>113.85</v>
       </c>
       <c r="G100">
         <v>34.3</v>
@@ -9993,37 +9993,37 @@
         <v>6.6</v>
       </c>
       <c r="M100">
-        <v>26.57466</v>
+        <v>26.84583</v>
       </c>
       <c r="N100">
-        <v>-19.97466</v>
+        <v>-20.24583</v>
       </c>
       <c r="O100">
-        <v>-3.2958189</v>
+        <v>-3.34056195</v>
       </c>
       <c r="P100">
-        <v>-16.6788411</v>
+        <v>-16.90526805</v>
       </c>
       <c r="Q100">
-        <v>-10.6788411</v>
+        <v>-10.90526805</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.495302330812168</v>
+        <v>2.944804661624336</v>
       </c>
       <c r="T100">
-        <v>28.25349838479871</v>
+        <v>56.50699676959743</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04097888740627349</v>
+        <v>0.04056495925065457</v>
       </c>
       <c r="W100">
-        <v>0.2261371783496007</v>
+        <v>0.2262347826086956</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -10031,91 +10031,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2483568933713546</v>
+        <v>0.245848237882755</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2534204813988521</v>
-      </c>
-      <c r="C101">
-        <v>-67.2438071570545</v>
-      </c>
-      <c r="D101">
-        <v>12.3061928429455</v>
-      </c>
-      <c r="E101">
-        <v>45.05</v>
-      </c>
-      <c r="F101">
-        <v>113.85</v>
-      </c>
-      <c r="G101">
-        <v>34.3</v>
-      </c>
-      <c r="H101">
-        <v>46.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>12.6</v>
-      </c>
-      <c r="K101">
-        <v>6</v>
-      </c>
-      <c r="L101">
-        <v>6.6</v>
-      </c>
-      <c r="M101">
-        <v>26.84583</v>
-      </c>
-      <c r="N101">
-        <v>-20.24583</v>
-      </c>
-      <c r="O101">
-        <v>-3.34056195</v>
-      </c>
-      <c r="P101">
-        <v>-16.90526805</v>
-      </c>
-      <c r="Q101">
-        <v>-10.90526805</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.944804661624336</v>
-      </c>
-      <c r="T101">
-        <v>56.50699676959743</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04056495925065457</v>
-      </c>
-      <c r="W101">
-        <v>0.2262347826086956</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.245848237882755</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
